--- a/database/event/1865/event_1865_evp_summary.xlsx
+++ b/database/event/1865/event_1865_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.7294</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9833</v>
+        <v>0.9413</v>
       </c>
       <c r="E2" t="n">
         <v>3.477</v>
@@ -548,7 +548,7 @@
         <v>1.6116</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="E3" t="n">
         <v>3.2403</v>
@@ -594,7 +594,7 @@
         <v>1.4852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7849</v>
+        <v>0.7457</v>
       </c>
       <c r="E4" t="n">
         <v>2.986</v>
@@ -640,7 +640,7 @@
         <v>1.4371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7459</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>2.8893</v>
@@ -686,7 +686,7 @@
         <v>1.3863</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7046</v>
+        <v>0.6666</v>
       </c>
       <c r="E6" t="n">
         <v>2.7873</v>
@@ -732,7 +732,7 @@
         <v>1.1708</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5296</v>
+        <v>0.4939</v>
       </c>
       <c r="E7" t="n">
         <v>2.3539</v>
@@ -778,7 +778,7 @@
         <v>1.028</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4136</v>
+        <v>0.3795</v>
       </c>
       <c r="E8" t="n">
         <v>2.0668</v>
@@ -824,7 +824,7 @@
         <v>0.9805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.375</v>
+        <v>0.3415</v>
       </c>
       <c r="E9" t="n">
         <v>1.9714</v>
@@ -870,7 +870,7 @@
         <v>0.8613</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2782</v>
+        <v>0.246</v>
       </c>
       <c r="E10" t="n">
         <v>1.7317</v>
@@ -916,7 +916,7 @@
         <v>0.8187</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2436</v>
+        <v>0.2119</v>
       </c>
       <c r="E11" t="n">
         <v>1.6461</v>
@@ -962,7 +962,7 @@
         <v>0.7969000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2259</v>
+        <v>0.1944</v>
       </c>
       <c r="E12" t="n">
         <v>1.6022</v>
@@ -1008,7 +1008,7 @@
         <v>0.4984</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0166</v>
+        <v>-0.0447</v>
       </c>
       <c r="E13" t="n">
         <v>1.002</v>
@@ -1054,7 +1054,7 @@
         <v>0.4922</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0216</v>
+        <v>-0.0497</v>
       </c>
       <c r="E14" t="n">
         <v>0.9895</v>
@@ -1100,7 +1100,7 @@
         <v>0.4305</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0717</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>0.8655</v>
@@ -1146,7 +1146,7 @@
         <v>0.3218</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.16</v>
+        <v>-0.1862</v>
       </c>
       <c r="E16" t="n">
         <v>0.6469</v>
@@ -1192,7 +1192,7 @@
         <v>0.2037</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2559</v>
+        <v>-0.2808</v>
       </c>
       <c r="E17" t="n">
         <v>0.4095</v>
@@ -1238,7 +1238,7 @@
         <v>0.1864</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.27</v>
+        <v>-0.2946</v>
       </c>
       <c r="E18" t="n">
         <v>0.3747</v>
@@ -1284,7 +1284,7 @@
         <v>0.1774</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2773</v>
+        <v>-0.3018</v>
       </c>
       <c r="E19" t="n">
         <v>0.3567</v>
@@ -1330,7 +1330,7 @@
         <v>0.0278</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3988</v>
+        <v>-0.4216</v>
       </c>
       <c r="E20" t="n">
         <v>0.0559</v>
@@ -1376,7 +1376,7 @@
         <v>0.0057</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4167</v>
+        <v>-0.4393</v>
       </c>
       <c r="E21" t="n">
         <v>0.0115</v>
@@ -1422,7 +1422,7 @@
         <v>-0.0709</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4789</v>
+        <v>-0.5007</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1425</v>
@@ -1468,7 +1468,7 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.479</v>
+        <v>-0.5008</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1427</v>
@@ -1514,7 +1514,7 @@
         <v>-0.07389999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4814</v>
+        <v>-0.5031</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1486</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1099</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.5319</v>
       </c>
       <c r="E25" t="n">
         <v>-0.2209</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1253</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5232</v>
+        <v>-0.5443</v>
       </c>
       <c r="E26" t="n">
         <v>-0.252</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1616</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5527</v>
+        <v>-0.5734</v>
       </c>
       <c r="E27" t="n">
         <v>-0.325</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1993</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5833</v>
+        <v>-0.6036</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4008</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2881</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6554</v>
+        <v>-0.6747</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5793</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6649</v>
+        <v>-0.6841</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6029</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3461</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7025</v>
+        <v>-0.7211</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6958</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4339</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7738</v>
+        <v>-0.7915</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8724</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4397</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7785</v>
+        <v>-0.7961</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8841</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4844</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8148</v>
+        <v>-0.8319</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9739</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4882</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8179</v>
+        <v>-0.8349</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9815</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E36" t="n">
         <v>-1</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E37" t="n">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E38" t="n">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5706</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8848</v>
+        <v>-0.901</v>
       </c>
       <c r="E39" t="n">
         <v>-1.1472</v>
@@ -2250,7 +2250,7 @@
         <v>-0.737</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.02</v>
+        <v>-1.0343</v>
       </c>
       <c r="E40" t="n">
         <v>-1.4818</v>
@@ -2296,7 +2296,7 @@
         <v>-1.0583</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2809</v>
+        <v>-1.2916</v>
       </c>
       <c r="E41" t="n">
         <v>-2.1277</v>

--- a/database/event/1865/event_1865_evp_summary.xlsx
+++ b/database/event/1865/event_1865_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.477</v>
+        <v>3.5721</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7294</v>
+        <v>1.7767</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9413</v>
+        <v>0.9746</v>
       </c>
       <c r="E2" t="n">
-        <v>3.477</v>
+        <v>3.5721</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3904</v>
+        <v>2.7322</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0866</v>
+        <v>0.8399</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3904</v>
+        <v>4.1402</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9375</v>
+        <v>2.1527</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0866</v>
+        <v>0.8399</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>116</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0241</v>
+        <v>2.9926</v>
       </c>
       <c r="N2" t="n">
         <v>194</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2403</v>
+        <v>3.5132</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6116</v>
+        <v>1.7474</v>
       </c>
       <c r="D3" t="n">
-        <v>0.847</v>
+        <v>0.948</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2403</v>
+        <v>3.5132</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3717</v>
+        <v>2.1733</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8686</v>
+        <v>1.3399</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3717</v>
+        <v>2.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1118</v>
+        <v>1.13</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8686</v>
+        <v>1.3399</v>
       </c>
       <c r="K3" t="n">
         <v>78</v>
@@ -575,7 +575,7 @@
         <v>116</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9804</v>
+        <v>2.4699</v>
       </c>
       <c r="N3" t="n">
         <v>194</v>
@@ -584,265 +584,265 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.986</v>
+        <v>3.2321</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4852</v>
+        <v>1.6076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7457</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.986</v>
+        <v>3.2321</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3378</v>
+        <v>2.4703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6482</v>
+        <v>0.7618</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3378</v>
+        <v>3.2174</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8948</v>
+        <v>1.6729</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6482</v>
+        <v>0.7618</v>
       </c>
       <c r="K4" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="L4" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="M4" t="n">
-        <v>2.543</v>
+        <v>2.4347</v>
       </c>
       <c r="N4" t="n">
-        <v>194</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8893</v>
+        <v>3.0636</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4371</v>
+        <v>1.5238</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8893</v>
+        <v>3.0636</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1066</v>
+        <v>2.6877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7827</v>
+        <v>0.3759</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1066</v>
+        <v>3.9836</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7075</v>
+        <v>2.0713</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7827</v>
+        <v>0.3759</v>
       </c>
       <c r="K5" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="L5" t="n">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4902</v>
+        <v>2.4472</v>
       </c>
       <c r="N5" t="n">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7873</v>
+        <v>2.8244</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3863</v>
+        <v>1.4048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6666</v>
+        <v>0.6371</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7873</v>
+        <v>2.8244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5153</v>
+        <v>2.7243</v>
       </c>
       <c r="G6" t="n">
-        <v>2.272</v>
+        <v>0.1001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5153</v>
+        <v>4.1123</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4177</v>
+        <v>2.1382</v>
       </c>
       <c r="J6" t="n">
-        <v>2.272</v>
+        <v>0.1001</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6897</v>
+        <v>2.2383</v>
       </c>
       <c r="N6" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3539</v>
+        <v>2.7872</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1708</v>
+        <v>1.3863</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4939</v>
+        <v>0.6203</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3539</v>
+        <v>2.7872</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3931</v>
+        <v>0.6604</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0392</v>
+        <v>2.1268</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3931</v>
+        <v>0.6604</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9397</v>
+        <v>0.3434</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0392</v>
+        <v>2.1268</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9005</v>
+        <v>2.4702</v>
       </c>
       <c r="N7" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.0668</v>
+        <v>2.5488</v>
       </c>
       <c r="C8" t="n">
-        <v>1.028</v>
+        <v>1.2677</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3795</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0668</v>
+        <v>2.5488</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0204</v>
+        <v>2.5304</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0872</v>
+        <v>0.0184</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0204</v>
+        <v>3.4291</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0165</v>
+        <v>1.783</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0872</v>
+        <v>0.0184</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L8" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0707</v>
+        <v>1.8014</v>
       </c>
       <c r="N8" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9714</v>
+        <v>2.2248</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9805</v>
+        <v>1.1066</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3415</v>
+        <v>0.3664</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9714</v>
+        <v>2.2248</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1497</v>
+        <v>2.6794</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1783</v>
+        <v>-0.4546</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1497</v>
+        <v>3.9542</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7424</v>
+        <v>2.056</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1783</v>
+        <v>-0.4546</v>
       </c>
       <c r="K9" t="n">
         <v>43</v>
@@ -851,7 +851,7 @@
         <v>53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5641</v>
+        <v>1.6014</v>
       </c>
       <c r="N9" t="n">
         <v>96</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7317</v>
+        <v>2.0807</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8613</v>
+        <v>1.0349</v>
       </c>
       <c r="D10" t="n">
-        <v>0.246</v>
+        <v>0.3013</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7317</v>
+        <v>2.0807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4142</v>
+        <v>2.1841</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3175</v>
+        <v>-0.1034</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4142</v>
+        <v>2.209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3357</v>
+        <v>1.1486</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3175</v>
+        <v>-0.1034</v>
       </c>
       <c r="K10" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L10" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6532</v>
+        <v>1.0452</v>
       </c>
       <c r="N10" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6461</v>
+        <v>2.0284</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8187</v>
+        <v>1.0089</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2119</v>
+        <v>0.2777</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6461</v>
+        <v>2.0284</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5532</v>
+        <v>0.6156</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1993</v>
+        <v>1.4128</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5532</v>
+        <v>0.6156</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4484</v>
+        <v>0.3201</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1993</v>
+        <v>1.4128</v>
       </c>
       <c r="K11" t="n">
         <v>65</v>
@@ -943,7 +943,7 @@
         <v>103</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7509</v>
+        <v>1.7329</v>
       </c>
       <c r="N11" t="n">
         <v>168</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6022</v>
+        <v>1.6612</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8262</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1944</v>
+        <v>0.1119</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6022</v>
+        <v>1.6612</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2394</v>
+        <v>-0.0383</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6372</v>
+        <v>1.6995</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2394</v>
+        <v>-0.0383</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8151</v>
+        <v>-0.0199</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6372</v>
+        <v>1.6995</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1779</v>
+        <v>1.6796</v>
       </c>
       <c r="N12" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.002</v>
+        <v>1.4467</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4984</v>
+        <v>0.7196</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0447</v>
+        <v>0.0151</v>
       </c>
       <c r="E13" t="n">
-        <v>1.002</v>
+        <v>1.4467</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9478</v>
+        <v>1.4457</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0542</v>
+        <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9478</v>
+        <v>1.4457</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7682</v>
+        <v>0.7517</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0542</v>
+        <v>0.001</v>
       </c>
       <c r="K13" t="n">
         <v>59</v>
@@ -1035,7 +1035,7 @@
         <v>66</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8224</v>
+        <v>0.7527</v>
       </c>
       <c r="N13" t="n">
         <v>125</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4922</v>
+        <v>0.5867</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0497</v>
+        <v>-0.1055</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9895</v>
+        <v>1.1795</v>
       </c>
       <c r="N14" t="n">
         <v>65</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8655</v>
+        <v>0.7305</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4305</v>
+        <v>0.3633</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.3082</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8655</v>
+        <v>0.7305</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2117</v>
+        <v>-0.9412</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3462</v>
+        <v>1.6717</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2117</v>
+        <v>-0.9412</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9821</v>
+        <v>-0.4894</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3462</v>
+        <v>1.6717</v>
       </c>
       <c r="K15" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6358999999999999</v>
+        <v>1.1823</v>
       </c>
       <c r="N15" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6469</v>
+        <v>0.5738</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3218</v>
+        <v>0.2854</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1862</v>
+        <v>-0.379</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6469</v>
+        <v>0.5738</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6469</v>
+        <v>1.2303</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6469</v>
+        <v>1.2303</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6469</v>
+        <v>0.6397</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="K16" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6469</v>
+        <v>-0.01679999999999993</v>
       </c>
       <c r="N16" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4095</v>
+        <v>0.5546</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2037</v>
+        <v>0.2758</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2808</v>
+        <v>-0.3876</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4095</v>
+        <v>0.5546</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0494</v>
+        <v>0.5546</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4589</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0494</v>
+        <v>0.5546</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04</v>
+        <v>0.5546</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4589</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L17" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4189</v>
+        <v>0.5546</v>
       </c>
       <c r="N17" t="n">
-        <v>168</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3747</v>
+        <v>0.4422</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1864</v>
+        <v>0.2199</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2946</v>
+        <v>-0.4384</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3747</v>
+        <v>0.4422</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3747</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3747</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3747</v>
+        <v>-0.0387</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3747</v>
+        <v>0.4778999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>65</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1774</v>
+        <v>0.1974</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3018</v>
+        <v>-0.4588</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3567</v>
+        <v>0.3969</v>
       </c>
       <c r="N19" t="n">
         <v>65</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0278</v>
+        <v>0.1955</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4216</v>
+        <v>-0.4606</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0559</v>
+        <v>0.393</v>
       </c>
       <c r="N20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0115</v>
+        <v>0.1768</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0057</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4393</v>
+        <v>-0.5582</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0115</v>
+        <v>0.1768</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9256</v>
+        <v>0.7468</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9141</v>
+        <v>-0.57</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9256</v>
+        <v>0.7468</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7502</v>
+        <v>0.3883</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9141</v>
+        <v>-0.57</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L21" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1639</v>
+        <v>-0.1817</v>
       </c>
       <c r="N21" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0709</v>
+        <v>0.0741</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5007</v>
+        <v>-0.5707</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1425</v>
+        <v>0.149</v>
       </c>
       <c r="N22" t="n">
         <v>43</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5008</v>
+        <v>-0.6253</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1427</v>
+        <v>0.0282</v>
       </c>
       <c r="N23" t="n">
         <v>59</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.0067</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5031</v>
+        <v>-0.6319</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1486</v>
+        <v>0.0135</v>
       </c>
       <c r="N24" t="n">
         <v>59</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1099</v>
+        <v>-0.0113</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5319</v>
+        <v>-0.6483</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2209</v>
+        <v>-0.0228</v>
       </c>
       <c r="N25" t="n">
         <v>59</v>
@@ -1596,173 +1596,173 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.252</v>
+        <v>-0.1211</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1253</v>
+        <v>-0.0602</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5443</v>
+        <v>-0.6927</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.252</v>
+        <v>-0.1211</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5266</v>
+        <v>-0.1211</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2746</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5266</v>
+        <v>-0.1211</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4268</v>
+        <v>-0.1211</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2746</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>59</v>
       </c>
       <c r="L26" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1522</v>
+        <v>-0.1211</v>
       </c>
       <c r="N26" t="n">
-        <v>125</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1616</v>
+        <v>-0.0672</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5734</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.325</v>
+        <v>-0.1352</v>
       </c>
       <c r="N27" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1993</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6036</v>
+        <v>-0.7183</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4008</v>
+        <v>-0.1778</v>
       </c>
       <c r="N28" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5793</v>
+        <v>-0.2249</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2881</v>
+        <v>-0.1119</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6747</v>
+        <v>-0.7395</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5793</v>
+        <v>-0.2249</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4207</v>
+        <v>-0.5958</v>
       </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>0.3709</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4207</v>
+        <v>-0.5958</v>
       </c>
       <c r="I29" t="n">
-        <v>0.341</v>
+        <v>-0.3098</v>
       </c>
       <c r="J29" t="n">
-        <v>-1</v>
+        <v>0.3709</v>
       </c>
       <c r="K29" t="n">
         <v>59</v>
@@ -1771,7 +1771,7 @@
         <v>66</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.659</v>
+        <v>0.06109999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2999</v>
+        <v>-0.2079</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6841</v>
+        <v>-0.8267</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6029</v>
+        <v>-0.418</v>
       </c>
       <c r="N30" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3461</v>
+        <v>-0.225</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7211</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6958</v>
+        <v>-0.4523</v>
       </c>
       <c r="N31" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4339</v>
+        <v>-0.2754</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7915</v>
+        <v>-0.888</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8724</v>
+        <v>-0.5537</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4397</v>
+        <v>-0.2847</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7961</v>
+        <v>-0.8965</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8841</v>
+        <v>-0.5725</v>
       </c>
       <c r="N33" t="n">
         <v>59</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4844</v>
+        <v>-0.3018</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8319</v>
+        <v>-0.912</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9739</v>
+        <v>-0.6068</v>
       </c>
       <c r="N34" t="n">
         <v>78</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4882</v>
+        <v>-0.3136</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8349</v>
+        <v>-0.9227</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9815</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>65</v>
@@ -2056,53 +2056,53 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1</v>
+        <v>-0.6352</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4974</v>
+        <v>-0.3159</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8423</v>
+        <v>-0.9248</v>
       </c>
       <c r="E36" t="n">
-        <v>-1</v>
+        <v>-0.6352</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>0.2269</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.8621</v>
       </c>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>0.2269</v>
       </c>
       <c r="I36" t="n">
-        <v>-1</v>
+        <v>0.118</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.8621</v>
       </c>
       <c r="K36" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-0.7441</v>
       </c>
       <c r="N36" t="n">
-        <v>43</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2112,7 +2112,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8423</v>
+        <v>-1.0895</v>
       </c>
       <c r="E37" t="n">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2158,7 +2158,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8423</v>
+        <v>-1.0895</v>
       </c>
       <c r="E38" t="n">
         <v>-1</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2188,53 +2188,53 @@
         <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1472</v>
+        <v>-1</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5706</v>
+        <v>-0.4974</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.901</v>
+        <v>-1.0895</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1472</v>
+        <v>-1</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0228</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1244</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.0228</v>
+        <v>-1</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0185</v>
+        <v>-1</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1244</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>78</v>
       </c>
       <c r="L39" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1429</v>
+        <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>194</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4818</v>
+        <v>-1.6066</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.737</v>
+        <v>-0.7991</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0343</v>
+        <v>-1.3633</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4818</v>
+        <v>-1.6066</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4818</v>
+        <v>-0.6066</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4818</v>
+        <v>-0.6066</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3905</v>
+        <v>-0.3154</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>66</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3905</v>
+        <v>-1.3154</v>
       </c>
       <c r="N40" t="n">
         <v>125</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1277</v>
+        <v>-2.1378</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0583</v>
+        <v>-1.0633</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2916</v>
+        <v>-1.6031</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1277</v>
+        <v>-2.1378</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2079</v>
+        <v>-1.2474</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9198</v>
+        <v>-0.8904</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2079</v>
+        <v>-1.2474</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.979</v>
+        <v>-0.6486</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9198</v>
+        <v>-0.8904</v>
       </c>
       <c r="K41" t="n">
         <v>78</v>
@@ -2323,7 +2323,7 @@
         <v>116</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8988</v>
+        <v>-1.539</v>
       </c>
       <c r="N41" t="n">
         <v>194</v>
@@ -2429,10 +2429,10 @@
         <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0725</v>
+        <v>0.0294</v>
       </c>
       <c r="J2" t="n">
-        <v>1.885</v>
+        <v>0.7644</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1939</v>
+        <v>-0.1615</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.0414</v>
+        <v>-4.199</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1939</v>
+        <v>-0.1615</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.0414</v>
+        <v>-4.199</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2446</v>
+        <v>-0.1928</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.3596</v>
+        <v>-5.0128</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.35</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9082</v>
+        <v>-0.6313</v>
       </c>
       <c r="J6" t="n">
-        <v>-23.6132</v>
+        <v>-16.4138</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1828</v>
+        <v>1.1132</v>
       </c>
       <c r="J7" t="n">
-        <v>30.7528</v>
+        <v>28.9432</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7926</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>20.6076</v>
+        <v>20.3528</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6466</v>
+        <v>0.6402</v>
       </c>
       <c r="J9" t="n">
-        <v>16.8116</v>
+        <v>16.6452</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0053</v>
+        <v>0.058</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1378</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7664</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-19.9264</v>
+        <v>-18.6212</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1285</v>
+        <v>-0.1185</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.084</v>
+        <v>-2.844</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1969</v>
+        <v>-0.1625</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.7256</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3015</v>
+        <v>-0.2231</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.236</v>
+        <v>-5.3544</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3823</v>
+        <v>-0.2601</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.1752</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5884</v>
+        <v>-0.3921</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.1216</v>
+        <v>-9.410399999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5478</v>
+        <v>1.356</v>
       </c>
       <c r="J17" t="n">
-        <v>37.1472</v>
+        <v>32.544</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7917</v>
+        <v>0.806</v>
       </c>
       <c r="J18" t="n">
-        <v>19.0008</v>
+        <v>19.344</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6926</v>
+        <v>0.7154</v>
       </c>
       <c r="J19" t="n">
-        <v>16.6224</v>
+        <v>17.1696</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0374</v>
+        <v>0.0375</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8976</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4315</v>
+        <v>-0.3543</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.356</v>
+        <v>-8.5032</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7049</v>
+        <v>1.197</v>
       </c>
       <c r="J22" t="n">
-        <v>39.2127</v>
+        <v>27.531</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0659</v>
+        <v>0.7884</v>
       </c>
       <c r="J23" t="n">
-        <v>24.5157</v>
+        <v>18.1332</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6271</v>
+        <v>0.5616</v>
       </c>
       <c r="J24" t="n">
-        <v>14.4233</v>
+        <v>12.9168</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4591</v>
+        <v>0.4644</v>
       </c>
       <c r="J25" t="n">
-        <v>10.5593</v>
+        <v>10.6812</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1695</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.8985</v>
+        <v>-1.9343</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.135</v>
+        <v>-0.1309</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.105</v>
+        <v>-3.0107</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2001</v>
+        <v>-0.1755</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.6023</v>
+        <v>-4.0365</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.67</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4603</v>
+        <v>-0.3225</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.5869</v>
+        <v>-7.4175</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.4149</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.1082</v>
+        <v>-9.5427</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.695</v>
+        <v>-0.4711</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.985</v>
+        <v>-10.8353</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.41</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1208</v>
+        <v>0.7935</v>
       </c>
       <c r="J32" t="n">
-        <v>33.624</v>
+        <v>23.805</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2704</v>
+        <v>0.2484</v>
       </c>
       <c r="J33" t="n">
-        <v>8.112</v>
+        <v>7.452</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2269</v>
+        <v>-0.1752</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.807</v>
+        <v>-5.256</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3884</v>
+        <v>-0.3317</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.652</v>
+        <v>-9.951000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5293</v>
+        <v>-0.4735</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.879</v>
+        <v>-14.205</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.23</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4351</v>
+        <v>0.4333</v>
       </c>
       <c r="J37" t="n">
-        <v>13.053</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.22</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4211</v>
+        <v>0.4226</v>
       </c>
       <c r="J38" t="n">
-        <v>12.633</v>
+        <v>12.678</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3488</v>
+        <v>0.3677</v>
       </c>
       <c r="J39" t="n">
-        <v>10.464</v>
+        <v>11.031</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5022</v>
+        <v>-0.3237</v>
       </c>
       <c r="J40" t="n">
-        <v>-15.066</v>
+        <v>-9.711</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.714</v>
+        <v>-0.481</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.42</v>
+        <v>-14.43</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.59</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7549</v>
+        <v>0.5417</v>
       </c>
       <c r="J42" t="n">
-        <v>15.8529</v>
+        <v>11.3757</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6028</v>
+        <v>0.4626</v>
       </c>
       <c r="J43" t="n">
-        <v>12.6588</v>
+        <v>9.714600000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5515</v>
+        <v>0.4379</v>
       </c>
       <c r="J44" t="n">
-        <v>11.5815</v>
+        <v>9.1959</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.26</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3248</v>
+        <v>0.3321</v>
       </c>
       <c r="J45" t="n">
-        <v>6.8208</v>
+        <v>6.9741</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.18</v>
       </c>
       <c r="I46" t="n">
-        <v>0.215</v>
+        <v>0.2383</v>
       </c>
       <c r="J46" t="n">
-        <v>4.515</v>
+        <v>5.0043</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0978</v>
+        <v>0.051</v>
       </c>
       <c r="J47" t="n">
-        <v>2.0538</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.72</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.323</v>
+        <v>-0.2641</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.783</v>
+        <v>-5.5461</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.55</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6153</v>
+        <v>-0.4223</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.9213</v>
+        <v>-8.8683</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.52</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.659</v>
+        <v>-0.4503</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.839</v>
+        <v>-9.456300000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.35</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8835</v>
+        <v>-0.6115</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.5535</v>
+        <v>-12.8415</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4054</v>
+        <v>0.4087</v>
       </c>
       <c r="J52" t="n">
-        <v>9.324199999999999</v>
+        <v>9.4001</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3685</v>
+        <v>-0.2727</v>
       </c>
       <c r="J53" t="n">
-        <v>-8.4755</v>
+        <v>-6.2721</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.391</v>
+        <v>-0.2816</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.993</v>
+        <v>-6.4768</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.58</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6113</v>
+        <v>-0.4112</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.0599</v>
+        <v>-9.457599999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.43</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.5511</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.5127</v>
+        <v>-12.6753</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.59</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3695</v>
+        <v>0.9665</v>
       </c>
       <c r="J57" t="n">
-        <v>31.4985</v>
+        <v>22.2295</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2527</v>
+        <v>0.8918</v>
       </c>
       <c r="J58" t="n">
-        <v>28.8121</v>
+        <v>20.5114</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.44</v>
       </c>
       <c r="I59" t="n">
-        <v>1.0696</v>
+        <v>0.7781</v>
       </c>
       <c r="J59" t="n">
-        <v>24.6008</v>
+        <v>17.8963</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0275</v>
+        <v>0.1046</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6325</v>
+        <v>2.4058</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9667</v>
+        <v>-0.9372</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.2341</v>
+        <v>-21.5556</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6222</v>
+        <v>0.6055</v>
       </c>
       <c r="J62" t="n">
-        <v>13.6884</v>
+        <v>13.321</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.72</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3322</v>
+        <v>-0.268</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.3084</v>
+        <v>-5.896</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.48</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7202</v>
+        <v>-0.4909</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.8444</v>
+        <v>-10.7998</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.47</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7336</v>
+        <v>-0.5004</v>
       </c>
       <c r="J65" t="n">
-        <v>-16.1392</v>
+        <v>-11.0088</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.26</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9949</v>
+        <v>-0.6995</v>
       </c>
       <c r="J66" t="n">
-        <v>-21.8878</v>
+        <v>-15.389</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.68</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4882</v>
+        <v>1.0507</v>
       </c>
       <c r="J67" t="n">
-        <v>32.7404</v>
+        <v>23.1154</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1176</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>24.5872</v>
+        <v>18.0862</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.44</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0108</v>
+        <v>0.7608</v>
       </c>
       <c r="J69" t="n">
-        <v>22.2376</v>
+        <v>16.7376</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.28</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6163</v>
+        <v>0.5591</v>
       </c>
       <c r="J70" t="n">
-        <v>13.5586</v>
+        <v>12.3002</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3097</v>
+        <v>-0.2221</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.8134</v>
+        <v>-4.8862</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.74</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5246</v>
+        <v>1.3637</v>
       </c>
       <c r="J72" t="n">
-        <v>27.4428</v>
+        <v>24.5466</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.7</v>
       </c>
       <c r="I73" t="n">
-        <v>1.4503</v>
+        <v>1.3184</v>
       </c>
       <c r="J73" t="n">
-        <v>26.1054</v>
+        <v>23.7312</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.64</v>
       </c>
       <c r="I74" t="n">
-        <v>1.335</v>
+        <v>1.2502</v>
       </c>
       <c r="J74" t="n">
-        <v>24.03</v>
+        <v>22.5036</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.39</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7893</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>14.2074</v>
+        <v>16.6482</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.26</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5102</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>9.1836</v>
+        <v>11.4228</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.03</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3667</v>
+        <v>0.49</v>
       </c>
       <c r="J77" t="n">
-        <v>6.6006</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7609</v>
+        <v>-0.531</v>
       </c>
       <c r="J78" t="n">
-        <v>-13.6962</v>
+        <v>-9.558</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.31</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.8931</v>
+        <v>-0.6207</v>
       </c>
       <c r="J79" t="n">
-        <v>-16.0758</v>
+        <v>-11.1726</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.31</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.8931</v>
+        <v>-0.6207</v>
       </c>
       <c r="J80" t="n">
-        <v>-16.0758</v>
+        <v>-11.1726</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.28</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9344</v>
+        <v>-0.6514</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.8192</v>
+        <v>-11.7252</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.49</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2071</v>
+        <v>1.1311</v>
       </c>
       <c r="J82" t="n">
-        <v>30.1775</v>
+        <v>28.2775</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.34</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8894</v>
+        <v>0.888</v>
       </c>
       <c r="J83" t="n">
-        <v>22.235</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4719</v>
+        <v>0.514</v>
       </c>
       <c r="J84" t="n">
-        <v>11.7975</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.413</v>
+        <v>0.4646</v>
       </c>
       <c r="J85" t="n">
-        <v>10.325</v>
+        <v>11.615</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.78</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7744</v>
+        <v>-0.724</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.36</v>
+        <v>-18.1</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.12</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3601</v>
+        <v>0.3958</v>
       </c>
       <c r="J87" t="n">
-        <v>9.0025</v>
+        <v>9.895</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2386</v>
+        <v>0.2334</v>
       </c>
       <c r="J88" t="n">
-        <v>5.965</v>
+        <v>5.835</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5092</v>
+        <v>-0.341</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.73</v>
+        <v>-8.525</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.774</v>
+        <v>-0.5275</v>
       </c>
       <c r="J90" t="n">
-        <v>-19.35</v>
+        <v>-13.1875</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.774</v>
+        <v>-0.5275</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.35</v>
+        <v>-13.1875</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5617</v>
+        <v>0.505</v>
       </c>
       <c r="J92" t="n">
-        <v>16.2893</v>
+        <v>14.645</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4794</v>
+        <v>0.4211</v>
       </c>
       <c r="J93" t="n">
-        <v>13.9026</v>
+        <v>12.2119</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1059</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>3.0711</v>
+        <v>1.8212</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.066</v>
+        <v>-0.0868</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.914</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2189</v>
+        <v>-1.2234</v>
       </c>
       <c r="J96" t="n">
-        <v>-35.3481</v>
+        <v>-35.4786</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8066</v>
+        <v>1.0004</v>
       </c>
       <c r="J97" t="n">
-        <v>23.3914</v>
+        <v>29.0116</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.211</v>
+        <v>0.237</v>
       </c>
       <c r="J98" t="n">
-        <v>6.119</v>
+        <v>6.873</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0863</v>
+        <v>0.1101</v>
       </c>
       <c r="J99" t="n">
-        <v>2.5027</v>
+        <v>3.1929</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4483</v>
+        <v>-0.2833</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.0007</v>
+        <v>-8.2157</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4483</v>
+        <v>-0.2833</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.0007</v>
+        <v>-8.2157</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7705</v>
+        <v>0.734</v>
       </c>
       <c r="J102" t="n">
-        <v>27.738</v>
+        <v>26.424</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3118</v>
+        <v>0.2806</v>
       </c>
       <c r="J103" t="n">
-        <v>11.2248</v>
+        <v>10.1016</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.026</v>
+        <v>0.0481</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.7316</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1437</v>
+        <v>-0.101</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.1732</v>
+        <v>-3.636</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5782</v>
+        <v>-0.5249</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.8152</v>
+        <v>-18.8964</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2704</v>
+        <v>0.2868</v>
       </c>
       <c r="J107" t="n">
-        <v>9.734400000000001</v>
+        <v>10.3248</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1829</v>
+        <v>0.1791</v>
       </c>
       <c r="J108" t="n">
-        <v>6.5844</v>
+        <v>6.4476</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1637</v>
+        <v>0.156</v>
       </c>
       <c r="J109" t="n">
-        <v>5.8932</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4241</v>
+        <v>-0.2704</v>
       </c>
       <c r="J110" t="n">
-        <v>-15.2676</v>
+        <v>-9.734400000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5332</v>
+        <v>-0.3472</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.1952</v>
+        <v>-12.4992</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2894</v>
+        <v>0.3022</v>
       </c>
       <c r="J112" t="n">
-        <v>7.8138</v>
+        <v>8.1594</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0257</v>
+        <v>-0.0446</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.6939</v>
+        <v>-1.2042</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1403</v>
+        <v>-0.1178</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.7881</v>
+        <v>-3.1806</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5913</v>
+        <v>-0.3916</v>
       </c>
       <c r="J115" t="n">
-        <v>-15.9651</v>
+        <v>-10.5732</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5913</v>
+        <v>-0.3916</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.9651</v>
+        <v>-10.5732</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9473</v>
+        <v>0.9334</v>
       </c>
       <c r="J117" t="n">
-        <v>25.5771</v>
+        <v>25.2018</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.33</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9029</v>
+        <v>0.8884</v>
       </c>
       <c r="J118" t="n">
-        <v>24.3783</v>
+        <v>23.9868</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8349</v>
+        <v>0.8179</v>
       </c>
       <c r="J119" t="n">
-        <v>22.5423</v>
+        <v>22.0833</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5596</v>
+        <v>-0.4964</v>
       </c>
       <c r="J120" t="n">
-        <v>-15.1092</v>
+        <v>-13.4028</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7574</v>
+        <v>-0.7076</v>
       </c>
       <c r="J121" t="n">
-        <v>-20.4498</v>
+        <v>-19.1052</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4217</v>
+        <v>0.3518</v>
       </c>
       <c r="J122" t="n">
-        <v>12.651</v>
+        <v>10.554</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3202</v>
+        <v>0.2622</v>
       </c>
       <c r="J123" t="n">
-        <v>9.606</v>
+        <v>7.866</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3048</v>
+        <v>0.249</v>
       </c>
       <c r="J124" t="n">
-        <v>9.144</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.307</v>
+        <v>-0.1836</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.210000000000001</v>
+        <v>-5.508</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3373</v>
+        <v>-0.2045</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.119</v>
+        <v>-6.135</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3475</v>
+        <v>0.2947</v>
       </c>
       <c r="J127" t="n">
-        <v>10.425</v>
+        <v>8.840999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2353</v>
+        <v>0.1864</v>
       </c>
       <c r="J128" t="n">
-        <v>7.059</v>
+        <v>5.592</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.296</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.352</v>
+        <v>-0.2213</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.56</v>
+        <v>-6.639</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5208</v>
+        <v>-0.3382</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.624</v>
+        <v>-10.146</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.96</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0527</v>
+        <v>0.0034</v>
       </c>
       <c r="J132" t="n">
-        <v>1.1067</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2702</v>
+        <v>-0.2241</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.6742</v>
+        <v>-4.7061</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.57</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.4118</v>
       </c>
       <c r="J134" t="n">
-        <v>-12.7344</v>
+        <v>-8.6478</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6486</v>
+        <v>-0.4399</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.6206</v>
+        <v>-9.2379</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7028</v>
+        <v>-0.4774</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.7588</v>
+        <v>-10.0254</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.7</v>
       </c>
       <c r="I137" t="n">
-        <v>1.547</v>
+        <v>1.3592</v>
       </c>
       <c r="J137" t="n">
-        <v>32.487</v>
+        <v>28.5432</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0379</v>
+        <v>1.0401</v>
       </c>
       <c r="J138" t="n">
-        <v>21.7959</v>
+        <v>21.8421</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8821</v>
+        <v>0.9196</v>
       </c>
       <c r="J139" t="n">
-        <v>18.5241</v>
+        <v>19.3116</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1014</v>
+        <v>0.186</v>
       </c>
       <c r="J140" t="n">
-        <v>2.1294</v>
+        <v>3.906</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0264</v>
+        <v>0.0552</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.5544</v>
+        <v>1.1592</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5833</v>
+        <v>0.5372</v>
       </c>
       <c r="J142" t="n">
-        <v>20.9988</v>
+        <v>19.3392</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1053</v>
+        <v>0.0911</v>
       </c>
       <c r="J143" t="n">
-        <v>3.7908</v>
+        <v>3.2796</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.049</v>
+        <v>0.0517</v>
       </c>
       <c r="J144" t="n">
-        <v>1.764</v>
+        <v>1.8612</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2437</v>
+        <v>-0.2004</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.773199999999999</v>
+        <v>-7.2144</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3731</v>
+        <v>-0.3232</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.4316</v>
+        <v>-11.6352</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2879</v>
+        <v>0.3143</v>
       </c>
       <c r="J147" t="n">
-        <v>10.3644</v>
+        <v>11.3148</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1055</v>
+        <v>0.0973</v>
       </c>
       <c r="J148" t="n">
-        <v>3.798</v>
+        <v>3.5028</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J149" t="n">
-        <v>2.016</v>
+        <v>1.5228</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2691</v>
+        <v>-0.1636</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.6876</v>
+        <v>-5.8896</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3472</v>
+        <v>-0.2155</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.4992</v>
+        <v>-7.758</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.49</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2161</v>
+        <v>1.1357</v>
       </c>
       <c r="J152" t="n">
-        <v>27.9703</v>
+        <v>26.1211</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6629</v>
+        <v>0.6606</v>
       </c>
       <c r="J153" t="n">
-        <v>15.2467</v>
+        <v>15.1938</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5847</v>
+        <v>0.5887</v>
       </c>
       <c r="J154" t="n">
-        <v>13.4481</v>
+        <v>13.5401</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0537</v>
+        <v>0.0134</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.2351</v>
+        <v>0.3082</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4395</v>
+        <v>-0.3671</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.1085</v>
+        <v>-8.443300000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.05</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2045</v>
+        <v>0.1927</v>
       </c>
       <c r="J157" t="n">
-        <v>4.7035</v>
+        <v>4.4321</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0001</v>
+        <v>-0.0288</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.0023</v>
+        <v>-0.6624</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3264</v>
+        <v>-0.2184</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.5072</v>
+        <v>-5.0232</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4365</v>
+        <v>-0.2861</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.0395</v>
+        <v>-6.5803</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.615</v>
+        <v>-0.4089</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.145</v>
+        <v>-9.4047</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1865/event_1865_evp_summary.xlsx
+++ b/database/event/1865/event_1865_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5721</v>
+        <v>3.5824</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7767</v>
+        <v>1.7818</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9746</v>
+        <v>1.0066</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5721</v>
+        <v>3.5824</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7322</v>
+        <v>2.6403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8399</v>
+        <v>0.9421</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1402</v>
+        <v>3.8173</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1527</v>
+        <v>2.0613</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8399</v>
+        <v>0.9421</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>116</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9926</v>
+        <v>3.0034</v>
       </c>
       <c r="N2" t="n">
         <v>194</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5132</v>
+        <v>3.491</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7474</v>
+        <v>1.7363</v>
       </c>
       <c r="D3" t="n">
-        <v>0.948</v>
+        <v>0.965</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5132</v>
+        <v>3.491</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1733</v>
+        <v>2.051</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3399</v>
+        <v>1.44</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1733</v>
+        <v>2.051</v>
       </c>
       <c r="I3" t="n">
-        <v>1.13</v>
+        <v>1.1075</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3399</v>
+        <v>1.44</v>
       </c>
       <c r="K3" t="n">
         <v>78</v>
@@ -575,7 +575,7 @@
         <v>116</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4699</v>
+        <v>2.5475</v>
       </c>
       <c r="N3" t="n">
         <v>194</v>
@@ -594,25 +594,25 @@
         <v>1.6076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8471</v>
       </c>
       <c r="E4" t="n">
         <v>3.2321</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4703</v>
+        <v>2.3872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7618</v>
+        <v>0.8449</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2174</v>
+        <v>2.9821</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6729</v>
+        <v>1.6103</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7618</v>
+        <v>0.8449</v>
       </c>
       <c r="K4" t="n">
         <v>59</v>
@@ -621,7 +621,7 @@
         <v>66</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4347</v>
+        <v>2.4552</v>
       </c>
       <c r="N4" t="n">
         <v>125</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0636</v>
+        <v>3.1137</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5238</v>
+        <v>1.5487</v>
       </c>
       <c r="D5" t="n">
-        <v>0.745</v>
+        <v>0.7932</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0636</v>
+        <v>3.1137</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6877</v>
+        <v>2.5931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3759</v>
+        <v>0.5206</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9836</v>
+        <v>3.6614</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0713</v>
+        <v>1.9771</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3759</v>
+        <v>0.5206</v>
       </c>
       <c r="K5" t="n">
         <v>78</v>
@@ -667,7 +667,7 @@
         <v>116</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4472</v>
+        <v>2.4977</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8244</v>
+        <v>2.9359</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4048</v>
+        <v>1.4602</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6371</v>
+        <v>0.7123</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8244</v>
+        <v>2.9359</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7243</v>
+        <v>0.6411</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1001</v>
+        <v>2.2948</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1123</v>
+        <v>0.6411</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1382</v>
+        <v>0.3462</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1001</v>
+        <v>2.2948</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2383</v>
+        <v>2.641</v>
       </c>
       <c r="N6" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7872</v>
+        <v>2.7667</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3863</v>
+        <v>1.3761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6203</v>
+        <v>0.6353</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7872</v>
+        <v>2.7667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6604</v>
+        <v>2.6442</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1268</v>
+        <v>0.1225</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6604</v>
+        <v>3.8299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3434</v>
+        <v>2.0681</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1268</v>
+        <v>0.1225</v>
       </c>
       <c r="K7" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L7" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4702</v>
+        <v>2.1906</v>
       </c>
       <c r="N7" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5488</v>
+        <v>2.5202</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2677</v>
+        <v>1.2535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5488</v>
+        <v>2.5202</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5304</v>
+        <v>2.4735</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0184</v>
+        <v>0.0467</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4291</v>
+        <v>3.2667</v>
       </c>
       <c r="I8" t="n">
-        <v>1.783</v>
+        <v>1.764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0184</v>
+        <v>0.0467</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -805,7 +805,7 @@
         <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8014</v>
+        <v>1.8107</v>
       </c>
       <c r="N8" t="n">
         <v>96</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2248</v>
+        <v>2.1005</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1066</v>
+        <v>1.0447</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3664</v>
+        <v>0.332</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2248</v>
+        <v>2.1005</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6794</v>
+        <v>2.5915</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4546</v>
+        <v>-0.491</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9542</v>
+        <v>3.656</v>
       </c>
       <c r="I9" t="n">
-        <v>2.056</v>
+        <v>1.9742</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4546</v>
+        <v>-0.491</v>
       </c>
       <c r="K9" t="n">
         <v>43</v>
@@ -851,7 +851,7 @@
         <v>53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6014</v>
+        <v>1.4832</v>
       </c>
       <c r="N9" t="n">
         <v>96</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0807</v>
+        <v>1.9942</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0349</v>
+        <v>0.9919</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3013</v>
+        <v>0.2836</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0807</v>
+        <v>1.9942</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1841</v>
+        <v>2.0898</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1034</v>
+        <v>-0.0956</v>
       </c>
       <c r="H10" t="n">
-        <v>2.209</v>
+        <v>2.0898</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1486</v>
+        <v>1.1285</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1034</v>
+        <v>-0.0956</v>
       </c>
       <c r="K10" t="n">
         <v>43</v>
@@ -897,7 +897,7 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0452</v>
+        <v>1.0329</v>
       </c>
       <c r="N10" t="n">
         <v>96</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0284</v>
+        <v>1.9558</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0089</v>
+        <v>0.9728</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2777</v>
+        <v>0.2661</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0284</v>
+        <v>1.9558</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6156</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4128</v>
+        <v>1.3999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6156</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3201</v>
+        <v>0.3002</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4128</v>
+        <v>1.3999</v>
       </c>
       <c r="K11" t="n">
         <v>65</v>
@@ -943,7 +943,7 @@
         <v>103</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7329</v>
+        <v>1.7001</v>
       </c>
       <c r="N11" t="n">
         <v>168</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6612</v>
+        <v>1.7774</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8262</v>
+        <v>0.884</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1119</v>
+        <v>0.1849</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6612</v>
+        <v>1.7774</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0383</v>
+        <v>-0.0357</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6995</v>
+        <v>1.8131</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0383</v>
+        <v>-0.0357</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0199</v>
+        <v>-0.0193</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6995</v>
+        <v>1.8131</v>
       </c>
       <c r="K12" t="n">
         <v>65</v>
@@ -989,7 +989,7 @@
         <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6796</v>
+        <v>1.7938</v>
       </c>
       <c r="N12" t="n">
         <v>168</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4467</v>
+        <v>1.3952</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7196</v>
+        <v>0.6939</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0151</v>
+        <v>0.0109</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4467</v>
+        <v>1.3952</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4457</v>
+        <v>1.3552</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001</v>
+        <v>0.04</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4457</v>
+        <v>1.3552</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7517</v>
+        <v>0.7318</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001</v>
+        <v>0.04</v>
       </c>
       <c r="K13" t="n">
         <v>59</v>
@@ -1035,7 +1035,7 @@
         <v>66</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7527</v>
+        <v>0.7718</v>
       </c>
       <c r="N13" t="n">
         <v>125</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5867</v>
+        <v>0.5649</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1055</v>
+        <v>-0.1072</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1795</v>
+        <v>1.1357</v>
       </c>
       <c r="N14" t="n">
         <v>65</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7305</v>
+        <v>1.0676</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3633</v>
+        <v>0.531</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3082</v>
+        <v>-0.1382</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7305</v>
+        <v>1.0676</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9412</v>
+        <v>-0.7804</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6717</v>
+        <v>1.848</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9412</v>
+        <v>-0.7804</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4894</v>
+        <v>-0.4214</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6717</v>
+        <v>1.848</v>
       </c>
       <c r="K15" t="n">
         <v>65</v>
@@ -1127,7 +1127,7 @@
         <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1823</v>
+        <v>1.4266</v>
       </c>
       <c r="N15" t="n">
         <v>168</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5738</v>
+        <v>0.5826</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2854</v>
+        <v>0.2898</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.379</v>
+        <v>-0.359</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5738</v>
+        <v>0.5826</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2303</v>
+        <v>1.2685</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6565</v>
+        <v>-0.6859</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2303</v>
+        <v>1.2685</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6397</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6565</v>
+        <v>-0.6859</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.01679999999999993</v>
+        <v>-0.0008999999999999009</v>
       </c>
       <c r="N16" t="n">
         <v>96</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2758</v>
+        <v>0.2658</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3876</v>
+        <v>-0.3809</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5546</v>
+        <v>0.5344</v>
       </c>
       <c r="N17" t="n">
         <v>78</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4422</v>
+        <v>0.5098</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2199</v>
+        <v>0.2536</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4384</v>
+        <v>-0.3921</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4422</v>
+        <v>0.5098</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0735</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5833</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0735</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0387</v>
+        <v>-0.0397</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5833</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
@@ -1265,7 +1265,7 @@
         <v>103</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4778999999999999</v>
+        <v>0.5436000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1974</v>
+        <v>0.2024</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4588</v>
+        <v>-0.4389</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3969</v>
+        <v>0.407</v>
       </c>
       <c r="N19" t="n">
         <v>65</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1955</v>
+        <v>0.2018</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4606</v>
+        <v>-0.4395</v>
       </c>
       <c r="E20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="F20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="I20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.393</v>
+        <v>0.4057</v>
       </c>
       <c r="N20" t="n">
         <v>65</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1768</v>
+        <v>0.1068</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0531</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5582</v>
+        <v>-0.5756</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1768</v>
+        <v>0.1068</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7468</v>
+        <v>0.6804</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.57</v>
+        <v>-0.5736</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7468</v>
+        <v>0.6804</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3883</v>
+        <v>0.3674</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.57</v>
+        <v>-0.5736</v>
       </c>
       <c r="K21" t="n">
         <v>59</v>
@@ -1403,7 +1403,7 @@
         <v>66</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1817</v>
+        <v>-0.2062</v>
       </c>
       <c r="N21" t="n">
         <v>125</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0741</v>
+        <v>0.0186</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5707</v>
+        <v>-0.6072</v>
       </c>
       <c r="E22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="F22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.149</v>
+        <v>0.0374</v>
       </c>
       <c r="N22" t="n">
         <v>43</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="C23" t="n">
-        <v>0.014</v>
+        <v>0.0062</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6253</v>
+        <v>-0.6185</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0282</v>
+        <v>0.0125</v>
       </c>
       <c r="N23" t="n">
         <v>59</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0067</v>
+        <v>0.0023</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6319</v>
+        <v>-0.6221</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0135</v>
+        <v>0.0047</v>
       </c>
       <c r="N24" t="n">
         <v>59</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0113</v>
+        <v>-0.0214</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6483</v>
+        <v>-0.6438</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0228</v>
+        <v>-0.043</v>
       </c>
       <c r="N25" t="n">
         <v>59</v>
@@ -1596,185 +1596,185 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1211</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0602</v>
+        <v>-0.0425</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6927</v>
+        <v>-0.6631</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1211</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1211</v>
+        <v>-0.5302</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4447</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1211</v>
+        <v>-0.5302</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1211</v>
+        <v>-0.2863</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4447</v>
       </c>
       <c r="K26" t="n">
         <v>59</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1211</v>
+        <v>0.1584</v>
       </c>
       <c r="N26" t="n">
-        <v>59</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0672</v>
+        <v>-0.0659</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.6845</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1352</v>
+        <v>-0.1325</v>
       </c>
       <c r="N27" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0867</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7183</v>
+        <v>-0.7035</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1778</v>
+        <v>-0.1743</v>
       </c>
       <c r="N28" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2249</v>
+        <v>-0.1999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1119</v>
+        <v>-0.0994</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7395</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2249</v>
+        <v>-0.1999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5958</v>
+        <v>-0.1999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5958</v>
+        <v>-0.1999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3098</v>
+        <v>-0.1999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="L29" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06109999999999999</v>
+        <v>-0.1999</v>
       </c>
       <c r="N29" t="n">
-        <v>125</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2079</v>
+        <v>-0.218</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8267</v>
+        <v>-0.8238</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.418</v>
+        <v>-0.4384</v>
       </c>
       <c r="N30" t="n">
         <v>43</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.225</v>
+        <v>-0.2493</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8524</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4523</v>
+        <v>-0.5012</v>
       </c>
       <c r="N31" t="n">
         <v>78</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2754</v>
+        <v>-0.2885</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.888</v>
+        <v>-0.8883</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5537</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2847</v>
+        <v>-0.2979</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8965</v>
+        <v>-0.8968</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5725</v>
+        <v>-0.5989</v>
       </c>
       <c r="N33" t="n">
         <v>59</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3018</v>
+        <v>-0.3076</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.912</v>
+        <v>-0.9058</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6068</v>
+        <v>-0.6185</v>
       </c>
       <c r="N34" t="n">
         <v>78</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3136</v>
+        <v>-0.3257</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9227</v>
+        <v>-0.9223</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6548</v>
       </c>
       <c r="N35" t="n">
         <v>65</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6352</v>
+        <v>-0.6694</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3159</v>
+        <v>-0.3329</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9248</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6352</v>
+        <v>-0.6694</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2269</v>
+        <v>0.1946</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8621</v>
+        <v>-0.864</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2269</v>
+        <v>0.1946</v>
       </c>
       <c r="I36" t="n">
-        <v>0.118</v>
+        <v>0.1051</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8621</v>
+        <v>-0.864</v>
       </c>
       <c r="K36" t="n">
         <v>78</v>
@@ -2093,7 +2093,7 @@
         <v>116</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7441</v>
+        <v>-0.7589</v>
       </c>
       <c r="N36" t="n">
         <v>194</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0895</v>
+        <v>-1.0794</v>
       </c>
       <c r="E37" t="n">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0895</v>
+        <v>-1.0794</v>
       </c>
       <c r="E38" t="n">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0895</v>
+        <v>-1.0794</v>
       </c>
       <c r="E39" t="n">
         <v>-1</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6066</v>
+        <v>-1.5304</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7991</v>
+        <v>-0.7612</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3633</v>
+        <v>-1.3209</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6066</v>
+        <v>-1.5304</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6066</v>
+        <v>-0.5382</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.9922</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6066</v>
+        <v>-0.5382</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3154</v>
+        <v>-0.2906</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.9922</v>
       </c>
       <c r="K40" t="n">
         <v>59</v>
@@ -2277,7 +2277,7 @@
         <v>66</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3154</v>
+        <v>-1.2828</v>
       </c>
       <c r="N40" t="n">
         <v>125</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1378</v>
+        <v>-1.88</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0633</v>
+        <v>-0.9351</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6031</v>
+        <v>-1.48</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1378</v>
+        <v>-1.88</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2474</v>
+        <v>-1.1322</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8904</v>
+        <v>-0.7478</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2474</v>
+        <v>-1.1322</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6486</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8904</v>
+        <v>-0.7478</v>
       </c>
       <c r="K41" t="n">
         <v>78</v>
@@ -2323,7 +2323,7 @@
         <v>116</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.539</v>
+        <v>-1.3592</v>
       </c>
       <c r="N41" t="n">
         <v>194</v>
@@ -2429,10 +2429,10 @@
         <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0294</v>
+        <v>0.0054</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7644</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1615</v>
+        <v>-0.1812</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.199</v>
+        <v>-4.7112</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1615</v>
+        <v>-0.1812</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.199</v>
+        <v>-4.7112</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1928</v>
+        <v>-0.2123</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.0128</v>
+        <v>-5.5198</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.35</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6313</v>
+        <v>-0.6309</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.4138</v>
+        <v>-16.4034</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1132</v>
+        <v>1.0959</v>
       </c>
       <c r="J7" t="n">
-        <v>28.9432</v>
+        <v>28.4934</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7412</v>
       </c>
       <c r="J8" t="n">
-        <v>20.3528</v>
+        <v>19.2712</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6402</v>
+        <v>0.6152</v>
       </c>
       <c r="J9" t="n">
-        <v>16.6452</v>
+        <v>15.9952</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="J10" t="n">
-        <v>1.508</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6637</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.6212</v>
+        <v>-17.2562</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1185</v>
+        <v>-0.1377</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.844</v>
+        <v>-3.3048</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1625</v>
+        <v>-0.182</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.9</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2231</v>
+        <v>-0.2423</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.3544</v>
+        <v>-5.8152</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2601</v>
+        <v>-0.2791</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.2424</v>
+        <v>-6.6984</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3921</v>
+        <v>-0.4065</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.410399999999999</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.356</v>
+        <v>1.4494</v>
       </c>
       <c r="J17" t="n">
-        <v>32.544</v>
+        <v>34.7856</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.806</v>
+        <v>0.7659</v>
       </c>
       <c r="J18" t="n">
-        <v>19.344</v>
+        <v>18.3816</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7154</v>
+        <v>0.6858</v>
       </c>
       <c r="J19" t="n">
-        <v>17.1696</v>
+        <v>16.4592</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0375</v>
+        <v>0.0607</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>1.4568</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3543</v>
+        <v>-0.3324</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.5032</v>
+        <v>-7.9776</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.197</v>
+        <v>1.3134</v>
       </c>
       <c r="J22" t="n">
-        <v>27.531</v>
+        <v>30.2082</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7884</v>
+        <v>0.8772</v>
       </c>
       <c r="J23" t="n">
-        <v>18.1332</v>
+        <v>20.1756</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5616</v>
+        <v>0.6274</v>
       </c>
       <c r="J24" t="n">
-        <v>12.9168</v>
+        <v>14.4302</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4644</v>
+        <v>0.5188</v>
       </c>
       <c r="J25" t="n">
-        <v>10.6812</v>
+        <v>11.9324</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0584</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.9343</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1309</v>
+        <v>-0.1549</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.0107</v>
+        <v>-3.5627</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1755</v>
+        <v>-0.1989</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.0365</v>
+        <v>-4.5747</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.67</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3225</v>
+        <v>-0.3422</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.4175</v>
+        <v>-7.8706</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4149</v>
+        <v>-0.4306</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.5427</v>
+        <v>-9.9038</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4711</v>
+        <v>-0.4834</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.8353</v>
+        <v>-11.1182</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.41</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7935</v>
+        <v>0.8686</v>
       </c>
       <c r="J32" t="n">
-        <v>23.805</v>
+        <v>26.058</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2484</v>
+        <v>0.2516</v>
       </c>
       <c r="J33" t="n">
-        <v>7.452</v>
+        <v>7.548</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1752</v>
+        <v>-0.1762</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.256</v>
+        <v>-5.286</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3317</v>
+        <v>-0.3234</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.951000000000001</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4735</v>
+        <v>-0.4529</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.205</v>
+        <v>-13.587</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.23</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4333</v>
+        <v>0.4773</v>
       </c>
       <c r="J37" t="n">
-        <v>12.999</v>
+        <v>14.319</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.22</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4226</v>
+        <v>0.4647</v>
       </c>
       <c r="J38" t="n">
-        <v>12.678</v>
+        <v>13.941</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3677</v>
+        <v>0.3878</v>
       </c>
       <c r="J39" t="n">
-        <v>11.031</v>
+        <v>11.634</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3237</v>
+        <v>-0.3361</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.711</v>
+        <v>-10.083</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.481</v>
+        <v>-0.487</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.43</v>
+        <v>-14.61</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.59</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5417</v>
+        <v>0.6239</v>
       </c>
       <c r="J42" t="n">
-        <v>11.3757</v>
+        <v>13.1019</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4626</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>9.714600000000001</v>
+        <v>11.1447</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4379</v>
+        <v>0.5014</v>
       </c>
       <c r="J44" t="n">
-        <v>9.1959</v>
+        <v>10.5294</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.26</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3321</v>
+        <v>0.3558</v>
       </c>
       <c r="J45" t="n">
-        <v>6.9741</v>
+        <v>7.4718</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.18</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2383</v>
+        <v>0.2608</v>
       </c>
       <c r="J46" t="n">
-        <v>5.0043</v>
+        <v>5.4768</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>0.051</v>
+        <v>0.0127</v>
       </c>
       <c r="J47" t="n">
-        <v>1.071</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.72</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2641</v>
+        <v>-0.2881</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.5461</v>
+        <v>-6.0501</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.55</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4223</v>
+        <v>-0.4394</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.8683</v>
+        <v>-9.227399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.52</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4503</v>
+        <v>-0.4657</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.456300000000001</v>
+        <v>-9.7797</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.35</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6115</v>
+        <v>-0.6153</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.8415</v>
+        <v>-12.9213</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4087</v>
+        <v>0.426</v>
       </c>
       <c r="J52" t="n">
-        <v>9.4001</v>
+        <v>9.798</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2727</v>
+        <v>-0.2928</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.2721</v>
+        <v>-6.7344</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2816</v>
+        <v>-0.3015</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.4768</v>
+        <v>-6.9345</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.58</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4112</v>
+        <v>-0.4261</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.457599999999999</v>
+        <v>-9.8003</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.43</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5511</v>
+        <v>-0.5574</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.6753</v>
+        <v>-12.8202</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.59</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9665</v>
+        <v>1.0653</v>
       </c>
       <c r="J57" t="n">
-        <v>22.2295</v>
+        <v>24.5019</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8918</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>20.5114</v>
+        <v>22.6642</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.44</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7781</v>
+        <v>0.8629</v>
       </c>
       <c r="J59" t="n">
-        <v>17.8963</v>
+        <v>19.8467</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1046</v>
+        <v>0.1276</v>
       </c>
       <c r="J60" t="n">
-        <v>2.4058</v>
+        <v>2.9348</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9372</v>
+        <v>-0.8539</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.5556</v>
+        <v>-19.6397</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6055</v>
+        <v>0.645</v>
       </c>
       <c r="J62" t="n">
-        <v>13.321</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.72</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.268</v>
+        <v>-0.2911</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.896</v>
+        <v>-6.4042</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.48</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4909</v>
+        <v>-0.5033</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.7998</v>
+        <v>-11.0726</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.47</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5004</v>
+        <v>-0.512</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.0088</v>
+        <v>-11.264</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.26</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6995</v>
+        <v>-0.6956</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.389</v>
+        <v>-15.3032</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.68</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0507</v>
+        <v>1.1595</v>
       </c>
       <c r="J67" t="n">
-        <v>23.1154</v>
+        <v>25.509</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.9144</v>
       </c>
       <c r="J68" t="n">
-        <v>18.0862</v>
+        <v>20.1168</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.44</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7608</v>
+        <v>0.8478</v>
       </c>
       <c r="J69" t="n">
-        <v>16.7376</v>
+        <v>18.6516</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.28</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5591</v>
+        <v>0.6252</v>
       </c>
       <c r="J70" t="n">
-        <v>12.3002</v>
+        <v>13.7544</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2221</v>
+        <v>-0.1997</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.8862</v>
+        <v>-4.3934</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.74</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3637</v>
+        <v>1.3541</v>
       </c>
       <c r="J72" t="n">
-        <v>24.5466</v>
+        <v>24.3738</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.7</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3184</v>
+        <v>1.3059</v>
       </c>
       <c r="J73" t="n">
-        <v>23.7312</v>
+        <v>23.5062</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.64</v>
       </c>
       <c r="I74" t="n">
-        <v>1.2502</v>
+        <v>1.2329</v>
       </c>
       <c r="J74" t="n">
-        <v>22.5036</v>
+        <v>22.1922</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.39</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>16.6482</v>
+        <v>15.8688</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.26</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>11.4228</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.03</v>
       </c>
       <c r="I77" t="n">
-        <v>0.49</v>
+        <v>0.3957</v>
       </c>
       <c r="J77" t="n">
-        <v>8.82</v>
+        <v>7.1226</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.531</v>
+        <v>-0.5456</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.558</v>
+        <v>-9.8208</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.31</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6207</v>
+        <v>-0.6274</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.1726</v>
+        <v>-11.2932</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.31</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6207</v>
+        <v>-0.6274</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.1726</v>
+        <v>-11.2932</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.28</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6514</v>
+        <v>-0.6552</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.7252</v>
+        <v>-11.7936</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.49</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1311</v>
+        <v>1.0926</v>
       </c>
       <c r="J82" t="n">
-        <v>28.2775</v>
+        <v>27.315</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.34</v>
       </c>
       <c r="I83" t="n">
-        <v>0.888</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>22.2</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
       <c r="J84" t="n">
-        <v>12.85</v>
+        <v>12.575</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4646</v>
+        <v>0.4581</v>
       </c>
       <c r="J85" t="n">
-        <v>11.615</v>
+        <v>11.4525</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.78</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.724</v>
+        <v>-0.6691</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.1</v>
+        <v>-16.7275</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.12</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3958</v>
+        <v>0.3713</v>
       </c>
       <c r="J87" t="n">
-        <v>9.895</v>
+        <v>9.282500000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2334</v>
+        <v>0.2168</v>
       </c>
       <c r="J88" t="n">
-        <v>5.835</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.341</v>
+        <v>-0.3583</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.525</v>
+        <v>-8.9575</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5275</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.1875</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5275</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.1875</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.505</v>
+        <v>0.4805</v>
       </c>
       <c r="J92" t="n">
-        <v>14.645</v>
+        <v>13.9345</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4211</v>
+        <v>0.4047</v>
       </c>
       <c r="J93" t="n">
-        <v>12.2119</v>
+        <v>11.7363</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>1.8212</v>
+        <v>1.8879</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0868</v>
+        <v>-0.0949</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.5172</v>
+        <v>-2.7521</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2234</v>
+        <v>-1.1111</v>
       </c>
       <c r="J96" t="n">
-        <v>-35.4786</v>
+        <v>-32.2219</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0004</v>
+        <v>0.953</v>
       </c>
       <c r="J97" t="n">
-        <v>29.0116</v>
+        <v>27.637</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.237</v>
+        <v>0.2457</v>
       </c>
       <c r="J98" t="n">
-        <v>6.873</v>
+        <v>7.1253</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1101</v>
+        <v>0.1204</v>
       </c>
       <c r="J99" t="n">
-        <v>3.1929</v>
+        <v>3.4916</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2833</v>
+        <v>-0.2951</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.2157</v>
+        <v>-8.5579</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2833</v>
+        <v>-0.2951</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.2157</v>
+        <v>-8.5579</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.734</v>
+        <v>0.6897</v>
       </c>
       <c r="J102" t="n">
-        <v>26.424</v>
+        <v>24.8292</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2806</v>
+        <v>0.2811</v>
       </c>
       <c r="J103" t="n">
-        <v>10.1016</v>
+        <v>10.1196</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0481</v>
+        <v>0.0552</v>
       </c>
       <c r="J104" t="n">
-        <v>1.7316</v>
+        <v>1.9872</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.101</v>
+        <v>-0.1045</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.636</v>
+        <v>-3.762</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5249</v>
+        <v>-0.4998</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.8964</v>
+        <v>-17.9928</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2868</v>
+        <v>0.2866</v>
       </c>
       <c r="J107" t="n">
-        <v>10.3248</v>
+        <v>10.3176</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1791</v>
+        <v>0.1827</v>
       </c>
       <c r="J108" t="n">
-        <v>6.4476</v>
+        <v>6.5772</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
       <c r="J109" t="n">
-        <v>5.616</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2704</v>
+        <v>-0.285</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.734400000000001</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3472</v>
+        <v>-0.3597</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.4992</v>
+        <v>-12.9492</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3022</v>
+        <v>0.2933</v>
       </c>
       <c r="J112" t="n">
-        <v>8.1594</v>
+        <v>7.9191</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0446</v>
+        <v>-0.0582</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.2042</v>
+        <v>-1.5714</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1178</v>
+        <v>-0.1344</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.1806</v>
+        <v>-3.6288</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3916</v>
+        <v>-0.4045</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.5732</v>
+        <v>-10.9215</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3916</v>
+        <v>-0.4045</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.5732</v>
+        <v>-10.9215</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9334</v>
+        <v>0.8719</v>
       </c>
       <c r="J117" t="n">
-        <v>25.2018</v>
+        <v>23.5413</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.33</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8884</v>
+        <v>0.8314</v>
       </c>
       <c r="J118" t="n">
-        <v>23.9868</v>
+        <v>22.4478</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8179</v>
+        <v>0.7699</v>
       </c>
       <c r="J119" t="n">
-        <v>22.0833</v>
+        <v>20.7873</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4964</v>
+        <v>-0.4689</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.4028</v>
+        <v>-12.6603</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7076</v>
+        <v>-0.6576</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.1052</v>
+        <v>-17.7552</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3518</v>
+        <v>0.3627</v>
       </c>
       <c r="J122" t="n">
-        <v>10.554</v>
+        <v>10.881</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2622</v>
+        <v>0.2758</v>
       </c>
       <c r="J123" t="n">
-        <v>7.866</v>
+        <v>8.273999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.249</v>
+        <v>0.2628</v>
       </c>
       <c r="J124" t="n">
-        <v>7.47</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1836</v>
+        <v>-0.1957</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.508</v>
+        <v>-5.871</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2045</v>
+        <v>-0.2167</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.135</v>
+        <v>-6.501</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2947</v>
+        <v>0.2973</v>
       </c>
       <c r="J127" t="n">
-        <v>8.840999999999999</v>
+        <v>8.919</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1864</v>
+        <v>0.1924</v>
       </c>
       <c r="J128" t="n">
-        <v>5.592</v>
+        <v>5.772</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.82</v>
+        <v>-3.207</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2213</v>
+        <v>-0.2365</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.639</v>
+        <v>-7.095</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3382</v>
+        <v>-0.351</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.146</v>
+        <v>-10.53</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.96</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0034</v>
+        <v>-0.0217</v>
       </c>
       <c r="J132" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.4557</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2241</v>
+        <v>-0.2473</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.7061</v>
+        <v>-5.1933</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.57</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4118</v>
+        <v>-0.4282</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.6478</v>
+        <v>-8.9922</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4399</v>
+        <v>-0.4546</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.2379</v>
+        <v>-9.5466</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4774</v>
+        <v>-0.4898</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.0254</v>
+        <v>-10.2858</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.7</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3592</v>
+        <v>1.3417</v>
       </c>
       <c r="J137" t="n">
-        <v>28.5432</v>
+        <v>28.1757</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0401</v>
+        <v>0.9941</v>
       </c>
       <c r="J138" t="n">
-        <v>21.8421</v>
+        <v>20.8761</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9196</v>
+        <v>0.8696</v>
       </c>
       <c r="J139" t="n">
-        <v>19.3116</v>
+        <v>18.2616</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.186</v>
+        <v>0.2085</v>
       </c>
       <c r="J140" t="n">
-        <v>3.906</v>
+        <v>4.3785</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0552</v>
+        <v>0.0837</v>
       </c>
       <c r="J141" t="n">
-        <v>1.1592</v>
+        <v>1.7577</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5372</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>19.3392</v>
+        <v>18.4896</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0911</v>
+        <v>0.0978</v>
       </c>
       <c r="J143" t="n">
-        <v>3.2796</v>
+        <v>3.5208</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0517</v>
+        <v>0.0576</v>
       </c>
       <c r="J144" t="n">
-        <v>1.8612</v>
+        <v>2.0736</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2004</v>
+        <v>-0.2024</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.2144</v>
+        <v>-7.2864</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3232</v>
+        <v>-0.3175</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6352</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3143</v>
+        <v>0.3155</v>
       </c>
       <c r="J147" t="n">
-        <v>11.3148</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0973</v>
+        <v>0.1039</v>
       </c>
       <c r="J148" t="n">
-        <v>3.5028</v>
+        <v>3.7404</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J149" t="n">
-        <v>1.5228</v>
+        <v>1.6776</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1636</v>
+        <v>-0.1777</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.8896</v>
+        <v>-6.3972</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2155</v>
+        <v>-0.2298</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.758</v>
+        <v>-8.2728</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.49</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1357</v>
+        <v>1.0967</v>
       </c>
       <c r="J152" t="n">
-        <v>26.1211</v>
+        <v>25.2241</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6606</v>
+        <v>0.634</v>
       </c>
       <c r="J153" t="n">
-        <v>15.1938</v>
+        <v>14.582</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5887</v>
+        <v>0.5698</v>
       </c>
       <c r="J154" t="n">
-        <v>13.5401</v>
+        <v>13.1054</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0134</v>
+        <v>0.0312</v>
       </c>
       <c r="J155" t="n">
-        <v>0.3082</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3671</v>
+        <v>-0.3482</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.443300000000001</v>
+        <v>-8.008599999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.05</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1927</v>
+        <v>0.1868</v>
       </c>
       <c r="J157" t="n">
-        <v>4.4321</v>
+        <v>4.2964</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0288</v>
+        <v>-0.0419</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.6624</v>
+        <v>-0.9637</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2184</v>
+        <v>-0.2364</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.0232</v>
+        <v>-5.4372</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2861</v>
+        <v>-0.303</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.5803</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4089</v>
+        <v>-0.4212</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.4047</v>
+        <v>-9.6876</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1865/event_1865_evp_summary.xlsx
+++ b/database/event/1865/event_1865_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5824</v>
+        <v>3.6457</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7818</v>
+        <v>1.8133</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0066</v>
+        <v>1.055</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5824</v>
+        <v>3.6457</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6403</v>
+        <v>2.6744</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9421</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8173</v>
+        <v>3.5982</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0613</v>
+        <v>2.0203</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9421</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>116</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0034</v>
+        <v>2.9916</v>
       </c>
       <c r="N2" t="n">
         <v>194</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.491</v>
+        <v>3.3373</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7363</v>
+        <v>1.6599</v>
       </c>
       <c r="D3" t="n">
-        <v>0.965</v>
+        <v>0.9145</v>
       </c>
       <c r="E3" t="n">
-        <v>3.491</v>
+        <v>3.3373</v>
       </c>
       <c r="F3" t="n">
-        <v>2.051</v>
+        <v>1.8619</v>
       </c>
       <c r="G3" t="n">
-        <v>1.44</v>
+        <v>1.4754</v>
       </c>
       <c r="H3" t="n">
-        <v>2.051</v>
+        <v>1.8619</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1075</v>
+        <v>1.0454</v>
       </c>
       <c r="J3" t="n">
-        <v>1.44</v>
+        <v>1.4754</v>
       </c>
       <c r="K3" t="n">
         <v>78</v>
@@ -575,7 +575,7 @@
         <v>116</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5475</v>
+        <v>2.5208</v>
       </c>
       <c r="N3" t="n">
         <v>194</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2321</v>
+        <v>3.29</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6076</v>
+        <v>1.6364</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8471</v>
+        <v>0.893</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2321</v>
+        <v>3.29</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3872</v>
+        <v>2.4653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8449</v>
+        <v>0.8247</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9821</v>
+        <v>2.8132</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6103</v>
+        <v>1.5795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8449</v>
+        <v>0.8247</v>
       </c>
       <c r="K4" t="n">
         <v>59</v>
@@ -621,7 +621,7 @@
         <v>66</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4552</v>
+        <v>2.4042</v>
       </c>
       <c r="N4" t="n">
         <v>125</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1137</v>
+        <v>3.1643</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5487</v>
+        <v>1.5738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7932</v>
+        <v>0.8357</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1137</v>
+        <v>3.1643</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5931</v>
+        <v>2.6638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5206</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6614</v>
+        <v>3.5585</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9771</v>
+        <v>1.998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5206</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>78</v>
@@ -667,7 +667,7 @@
         <v>116</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4977</v>
+        <v>2.4985</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9359</v>
+        <v>2.7885</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4602</v>
+        <v>1.3869</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7123</v>
+        <v>0.6645</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9359</v>
+        <v>2.7885</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6411</v>
+        <v>0.5154</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2948</v>
+        <v>2.2731</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6411</v>
+        <v>0.5154</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3462</v>
+        <v>0.2894</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2948</v>
+        <v>2.2731</v>
       </c>
       <c r="K6" t="n">
         <v>65</v>
@@ -713,7 +713,7 @@
         <v>103</v>
       </c>
       <c r="M6" t="n">
-        <v>2.641</v>
+        <v>2.5625</v>
       </c>
       <c r="N6" t="n">
         <v>168</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7667</v>
+        <v>2.7828</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3761</v>
+        <v>1.3841</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6353</v>
+        <v>0.6619</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7667</v>
+        <v>2.7828</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6442</v>
+        <v>2.6964</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1225</v>
+        <v>0.0864</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8299</v>
+        <v>3.6809</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0681</v>
+        <v>2.0667</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1225</v>
+        <v>0.0864</v>
       </c>
       <c r="K7" t="n">
         <v>43</v>
@@ -759,7 +759,7 @@
         <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1906</v>
+        <v>2.1531</v>
       </c>
       <c r="N7" t="n">
         <v>96</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5202</v>
+        <v>2.5575</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2535</v>
+        <v>1.272</v>
       </c>
       <c r="D8" t="n">
-        <v>0.523</v>
+        <v>0.5593</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5202</v>
+        <v>2.5575</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4735</v>
+        <v>2.547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0467</v>
+        <v>0.0105</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2667</v>
+        <v>3.12</v>
       </c>
       <c r="I8" t="n">
-        <v>1.764</v>
+        <v>1.7518</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0467</v>
+        <v>0.0105</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -805,7 +805,7 @@
         <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8107</v>
+        <v>1.7623</v>
       </c>
       <c r="N8" t="n">
         <v>96</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1005</v>
+        <v>2.1967</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0447</v>
+        <v>1.0926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.332</v>
+        <v>0.3949</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1005</v>
+        <v>2.1967</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5915</v>
+        <v>2.6557</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.491</v>
+        <v>-0.459</v>
       </c>
       <c r="H9" t="n">
-        <v>3.656</v>
+        <v>3.5279</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9742</v>
+        <v>1.9808</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.491</v>
+        <v>-0.459</v>
       </c>
       <c r="K9" t="n">
         <v>43</v>
@@ -851,7 +851,7 @@
         <v>53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4832</v>
+        <v>1.5218</v>
       </c>
       <c r="N9" t="n">
         <v>96</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9942</v>
+        <v>1.9211</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9919</v>
+        <v>0.9555</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2836</v>
+        <v>0.2694</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9942</v>
+        <v>1.9211</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0898</v>
+        <v>0.5017</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0956</v>
+        <v>1.4194</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0898</v>
+        <v>0.5017</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1285</v>
+        <v>0.2817</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0956</v>
+        <v>1.4194</v>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L10" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0329</v>
+        <v>1.7011</v>
       </c>
       <c r="N10" t="n">
-        <v>96</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9558</v>
+        <v>1.7637</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9728</v>
+        <v>0.8772</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2661</v>
+        <v>0.1977</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9558</v>
+        <v>1.7637</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.0349</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3999</v>
+        <v>1.7986</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.0349</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3002</v>
+        <v>-0.0196</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3999</v>
+        <v>1.7986</v>
       </c>
       <c r="K11" t="n">
         <v>65</v>
@@ -943,7 +943,7 @@
         <v>103</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7001</v>
+        <v>1.779</v>
       </c>
       <c r="N11" t="n">
         <v>168</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7774</v>
+        <v>1.7594</v>
       </c>
       <c r="C12" t="n">
-        <v>0.884</v>
+        <v>0.8751</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1849</v>
+        <v>0.1957</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7774</v>
+        <v>1.7594</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0357</v>
+        <v>1.9071</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8131</v>
+        <v>-0.1477</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0357</v>
+        <v>1.9071</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0193</v>
+        <v>1.0708</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8131</v>
+        <v>-0.1477</v>
       </c>
       <c r="K12" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7938</v>
+        <v>0.9231</v>
       </c>
       <c r="N12" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3952</v>
+        <v>1.2321</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6939</v>
+        <v>0.6128</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0109</v>
+        <v>-0.0445</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3952</v>
+        <v>1.2321</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3552</v>
+        <v>1.204</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04</v>
+        <v>0.0281</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3552</v>
+        <v>1.204</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7318</v>
+        <v>0.676</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04</v>
+        <v>0.0281</v>
       </c>
       <c r="K13" t="n">
         <v>59</v>
@@ -1035,7 +1035,7 @@
         <v>66</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7718</v>
+        <v>0.7041000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>125</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5649</v>
+        <v>0.5212</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1072</v>
+        <v>-0.1284</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1357</v>
+        <v>1.048</v>
       </c>
       <c r="N14" t="n">
         <v>65</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0676</v>
+        <v>1.0003</v>
       </c>
       <c r="C15" t="n">
-        <v>0.531</v>
+        <v>0.4975</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1382</v>
+        <v>-0.1501</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0676</v>
+        <v>1.0003</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7804</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.848</v>
+        <v>1.8294</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7804</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4214</v>
+        <v>-0.4655</v>
       </c>
       <c r="J15" t="n">
-        <v>1.848</v>
+        <v>1.8294</v>
       </c>
       <c r="K15" t="n">
         <v>65</v>
@@ -1127,7 +1127,7 @@
         <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4266</v>
+        <v>1.3639</v>
       </c>
       <c r="N15" t="n">
         <v>168</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5826</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2898</v>
+        <v>0.3231</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.359</v>
+        <v>-0.3098</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5826</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2685</v>
+        <v>1.3198</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6859</v>
+        <v>-0.6701</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2685</v>
+        <v>1.3198</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.741</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6859</v>
+        <v>-0.6701</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0008999999999999009</v>
+        <v>0.07089999999999996</v>
       </c>
       <c r="N16" t="n">
         <v>96</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5344</v>
+        <v>0.5709</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2658</v>
+        <v>0.284</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3809</v>
+        <v>-0.3457</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5344</v>
+        <v>0.5709</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5344</v>
+        <v>-0.0591</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5344</v>
+        <v>-0.0591</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5344</v>
+        <v>-0.0332</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="K17" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5344</v>
+        <v>0.5968</v>
       </c>
       <c r="N17" t="n">
-        <v>78</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5098</v>
+        <v>0.4491</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2536</v>
+        <v>0.2234</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3921</v>
+        <v>-0.4012</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5098</v>
+        <v>0.4491</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0735</v>
+        <v>0.4491</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5833</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0735</v>
+        <v>0.4491</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0397</v>
+        <v>0.4491</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5833</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L18" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5436000000000001</v>
+        <v>0.4491</v>
       </c>
       <c r="N18" t="n">
-        <v>168</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2024</v>
+        <v>0.1625</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4389</v>
+        <v>-0.457</v>
       </c>
       <c r="E19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="F19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="I19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.407</v>
+        <v>0.3267</v>
       </c>
       <c r="N19" t="n">
         <v>65</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2018</v>
+        <v>0.1601</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4395</v>
+        <v>-0.4591</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4057</v>
+        <v>0.3219</v>
       </c>
       <c r="N20" t="n">
         <v>65</v>
@@ -1366,124 +1366,124 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1068</v>
+        <v>0.1205</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0531</v>
+        <v>0.0599</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5756</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1068</v>
+        <v>0.1205</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6804</v>
+        <v>0.1205</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5736</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6804</v>
+        <v>0.1205</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3674</v>
+        <v>0.1205</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5736</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2062</v>
+        <v>0.1205</v>
       </c>
       <c r="N21" t="n">
-        <v>125</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0374</v>
+        <v>0.0369</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0186</v>
+        <v>0.0184</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6072</v>
+        <v>-0.589</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0374</v>
+        <v>0.0369</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0374</v>
+        <v>0.6538</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.6169</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0374</v>
+        <v>0.6538</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0374</v>
+        <v>0.3671</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.6169</v>
       </c>
       <c r="K22" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0374</v>
+        <v>-0.2498</v>
       </c>
       <c r="N22" t="n">
-        <v>43</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0062</v>
+        <v>-0.0007</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6185</v>
+        <v>-0.6065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="N23" t="n">
         <v>59</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0023</v>
+        <v>-0.0109</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6221</v>
+        <v>-0.6158</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0047</v>
+        <v>-0.0219</v>
       </c>
       <c r="N24" t="n">
         <v>59</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0214</v>
+        <v>-0.0297</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6438</v>
+        <v>-0.633</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.043</v>
+        <v>-0.0597</v>
       </c>
       <c r="N25" t="n">
         <v>59</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0425</v>
+        <v>-0.0403</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6631</v>
+        <v>-0.6427</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5302</v>
+        <v>-0.4538</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4447</v>
+        <v>0.3728</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5302</v>
+        <v>-0.4538</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2863</v>
+        <v>-0.2548</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4447</v>
+        <v>0.3728</v>
       </c>
       <c r="K26" t="n">
         <v>59</v>
@@ -1633,7 +1633,7 @@
         <v>66</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1584</v>
+        <v>0.118</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0659</v>
+        <v>-0.0704</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6845</v>
+        <v>-0.6702</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1325</v>
+        <v>-0.1415</v>
       </c>
       <c r="N27" t="n">
         <v>59</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0867</v>
+        <v>-0.1095</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7035</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1743</v>
+        <v>-0.2202</v>
       </c>
       <c r="N28" t="n">
         <v>43</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0994</v>
+        <v>-0.1176</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7135</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1999</v>
+        <v>-0.2364</v>
       </c>
       <c r="N29" t="n">
         <v>78</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.218</v>
+        <v>-0.2267</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8238</v>
+        <v>-0.8134</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4384</v>
+        <v>-0.4557</v>
       </c>
       <c r="N30" t="n">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2493</v>
+        <v>-0.244</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8524</v>
+        <v>-0.8292</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5012</v>
+        <v>-0.4905</v>
       </c>
       <c r="N31" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2885</v>
+        <v>-0.2703</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8883</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2979</v>
+        <v>-0.2831</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8968</v>
+        <v>-0.865</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5989</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>59</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6185</v>
+        <v>-0.5988</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3076</v>
+        <v>-0.2978</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9058</v>
+        <v>-0.8786</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6185</v>
+        <v>-0.5988</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6185</v>
+        <v>0.2504</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.8492</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6185</v>
+        <v>0.2504</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6185</v>
+        <v>0.1406</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.8492</v>
       </c>
       <c r="K34" t="n">
         <v>78</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6185</v>
+        <v>-0.7085999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>78</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3257</v>
+        <v>-0.3097</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9223</v>
+        <v>-0.8894</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6548</v>
+        <v>-0.6226</v>
       </c>
       <c r="N35" t="n">
         <v>65</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6694</v>
+        <v>-0.6575</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3329</v>
+        <v>-0.327</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.9053</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6694</v>
+        <v>-0.6575</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1946</v>
+        <v>-0.6575</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.864</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1946</v>
+        <v>-0.6575</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1051</v>
+        <v>-0.6575</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.864</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>78</v>
       </c>
       <c r="L36" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7589</v>
+        <v>-0.6575</v>
       </c>
       <c r="N36" t="n">
-        <v>194</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37">
@@ -2112,7 +2112,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0794</v>
+        <v>-1.0613</v>
       </c>
       <c r="E37" t="n">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0794</v>
+        <v>-1.0613</v>
       </c>
       <c r="E38" t="n">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4974</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0794</v>
+        <v>-1.0613</v>
       </c>
       <c r="E39" t="n">
         <v>-1</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5304</v>
+        <v>-1.4713</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7612</v>
+        <v>-0.7318</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3209</v>
+        <v>-1.276</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5304</v>
+        <v>-1.4713</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5382</v>
+        <v>-0.4713</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9922</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5382</v>
+        <v>-0.4713</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2906</v>
+        <v>-0.2646</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9922</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
         <v>59</v>
@@ -2277,7 +2277,7 @@
         <v>66</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2828</v>
+        <v>-1.2646</v>
       </c>
       <c r="N40" t="n">
         <v>125</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.88</v>
+        <v>-1.7484</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9351</v>
+        <v>-0.8696</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.48</v>
+        <v>-1.4023</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.88</v>
+        <v>-1.7484</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1322</v>
+        <v>-1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7478</v>
+        <v>-0.7084</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1322</v>
+        <v>-1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5839</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7478</v>
+        <v>-0.7084</v>
       </c>
       <c r="K41" t="n">
         <v>78</v>
@@ -2323,7 +2323,7 @@
         <v>116</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3592</v>
+        <v>-1.2923</v>
       </c>
       <c r="N41" t="n">
         <v>194</v>
@@ -2429,10 +2429,10 @@
         <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0054</v>
+        <v>0.0138</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1404</v>
+        <v>0.3588</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1812</v>
+        <v>-0.1652</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.7112</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1812</v>
+        <v>-0.1652</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.7112</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2123</v>
+        <v>-0.196</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.5198</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.35</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6309</v>
+        <v>-0.6503</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.4034</v>
+        <v>-16.9078</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0959</v>
+        <v>1.0983</v>
       </c>
       <c r="J7" t="n">
-        <v>28.4934</v>
+        <v>28.5558</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7412</v>
+        <v>0.7118</v>
       </c>
       <c r="J8" t="n">
-        <v>19.2712</v>
+        <v>18.5068</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6152</v>
+        <v>0.5803</v>
       </c>
       <c r="J9" t="n">
-        <v>15.9952</v>
+        <v>15.0878</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.075</v>
+        <v>0.0585</v>
       </c>
       <c r="J10" t="n">
-        <v>1.95</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6637</v>
+        <v>-0.6312</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.2562</v>
+        <v>-16.4112</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1377</v>
+        <v>-0.1224</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3048</v>
+        <v>-2.9376</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.182</v>
+        <v>-0.1659</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.368</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.79</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2423</v>
+        <v>-0.2255</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.8152</v>
+        <v>-5.412</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2791</v>
+        <v>-0.2622</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6984</v>
+        <v>-6.2928</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4065</v>
+        <v>-0.3955</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.756</v>
+        <v>-9.492000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4494</v>
+        <v>1.4853</v>
       </c>
       <c r="J17" t="n">
-        <v>34.7856</v>
+        <v>35.6472</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7659</v>
+        <v>0.7412</v>
       </c>
       <c r="J18" t="n">
-        <v>18.3816</v>
+        <v>17.7888</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6858</v>
+        <v>0.6575</v>
       </c>
       <c r="J19" t="n">
-        <v>16.4592</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0607</v>
+        <v>0.0445</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4568</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3324</v>
+        <v>-0.293</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.9776</v>
+        <v>-7.032</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3134</v>
+        <v>1.3168</v>
       </c>
       <c r="J22" t="n">
-        <v>30.2082</v>
+        <v>30.2864</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8772</v>
+        <v>0.8647</v>
       </c>
       <c r="J23" t="n">
-        <v>20.1756</v>
+        <v>19.8881</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6274</v>
+        <v>0.6212</v>
       </c>
       <c r="J24" t="n">
-        <v>14.4302</v>
+        <v>14.2876</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5188</v>
+        <v>0.5141</v>
       </c>
       <c r="J25" t="n">
-        <v>11.9324</v>
+        <v>11.8243</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0584</v>
+        <v>-0.0549</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3432</v>
+        <v>-1.2627</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1549</v>
+        <v>-0.1387</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.5627</v>
+        <v>-3.1901</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1989</v>
+        <v>-0.1835</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.5747</v>
+        <v>-4.2205</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.67</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3422</v>
+        <v>-0.3295</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.8706</v>
+        <v>-7.5785</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4306</v>
+        <v>-0.422</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.9038</v>
+        <v>-9.706</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4834</v>
+        <v>-0.4798</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.1182</v>
+        <v>-11.0354</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.41</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8686</v>
+        <v>0.8547</v>
       </c>
       <c r="J32" t="n">
-        <v>26.058</v>
+        <v>25.641</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2516</v>
+        <v>0.2152</v>
       </c>
       <c r="J33" t="n">
-        <v>7.548</v>
+        <v>6.456</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1762</v>
+        <v>-0.143</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.286</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3234</v>
+        <v>-0.2815</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.702</v>
+        <v>-8.445</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4529</v>
+        <v>-0.41</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.587</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.23</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4773</v>
+        <v>0.4325</v>
       </c>
       <c r="J37" t="n">
-        <v>14.319</v>
+        <v>12.975</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.22</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4647</v>
+        <v>0.4159</v>
       </c>
       <c r="J38" t="n">
-        <v>13.941</v>
+        <v>12.477</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3878</v>
+        <v>0.3321</v>
       </c>
       <c r="J39" t="n">
-        <v>11.634</v>
+        <v>9.962999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3361</v>
+        <v>-0.3203</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.083</v>
+        <v>-9.609</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.54</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.487</v>
+        <v>-0.4866</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.61</v>
+        <v>-14.598</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.59</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6239</v>
+        <v>0.5851</v>
       </c>
       <c r="J42" t="n">
-        <v>13.1019</v>
+        <v>12.2871</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.46</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.4941</v>
       </c>
       <c r="J43" t="n">
-        <v>11.1447</v>
+        <v>10.3761</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5014</v>
+        <v>0.458</v>
       </c>
       <c r="J44" t="n">
-        <v>10.5294</v>
+        <v>9.618</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.26</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3558</v>
+        <v>0.3017</v>
       </c>
       <c r="J45" t="n">
-        <v>7.4718</v>
+        <v>6.3357</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.18</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2608</v>
+        <v>0.2149</v>
       </c>
       <c r="J46" t="n">
-        <v>5.4768</v>
+        <v>4.5129</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.97</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0127</v>
+        <v>0.0431</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2667</v>
+        <v>0.9051</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.72</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2881</v>
+        <v>-0.276</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.0501</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.55</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4394</v>
+        <v>-0.4324</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.227399999999999</v>
+        <v>-9.080399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.52</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4657</v>
+        <v>-0.4607</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.7797</v>
+        <v>-9.6747</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.35</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6153</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.9213</v>
+        <v>-13.2195</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.426</v>
+        <v>0.3902</v>
       </c>
       <c r="J52" t="n">
-        <v>9.798</v>
+        <v>8.974600000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2928</v>
+        <v>-0.2781</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.7344</v>
+        <v>-6.3963</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.72</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3015</v>
+        <v>-0.2869</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.9345</v>
+        <v>-6.5987</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.58</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4261</v>
+        <v>-0.4169</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.8003</v>
+        <v>-9.588699999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.43</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5574</v>
+        <v>-0.5636</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.8202</v>
+        <v>-12.9628</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.59</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0653</v>
+        <v>1.055</v>
       </c>
       <c r="J57" t="n">
-        <v>24.5019</v>
+        <v>24.265</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9725</v>
       </c>
       <c r="J58" t="n">
-        <v>22.6642</v>
+        <v>22.3675</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.44</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8629</v>
+        <v>0.8482</v>
       </c>
       <c r="J59" t="n">
-        <v>19.8467</v>
+        <v>19.5086</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1276</v>
+        <v>0.104</v>
       </c>
       <c r="J60" t="n">
-        <v>2.9348</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8539</v>
+        <v>-0.8407</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.6397</v>
+        <v>-19.3361</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="I62" t="n">
-        <v>0.645</v>
+        <v>0.6536</v>
       </c>
       <c r="J62" t="n">
-        <v>14.19</v>
+        <v>14.3792</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.72</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2911</v>
+        <v>-0.2789</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.4042</v>
+        <v>-6.1358</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.48</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5033</v>
+        <v>-0.5017</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.0726</v>
+        <v>-11.0374</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.47</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.512</v>
+        <v>-0.5115</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.264</v>
+        <v>-11.253</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.26</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6956</v>
+        <v>-0.7256</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.3032</v>
+        <v>-15.9632</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.68</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1595</v>
+        <v>1.1537</v>
       </c>
       <c r="J67" t="n">
-        <v>25.509</v>
+        <v>25.3814</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9144</v>
+        <v>0.9025</v>
       </c>
       <c r="J68" t="n">
-        <v>20.1168</v>
+        <v>19.855</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.44</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8478</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>18.6516</v>
+        <v>18.3964</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.28</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6252</v>
+        <v>0.6197</v>
       </c>
       <c r="J70" t="n">
-        <v>13.7544</v>
+        <v>13.6334</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1997</v>
+        <v>-0.1716</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.3934</v>
+        <v>-3.7752</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.74</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3541</v>
+        <v>1.3788</v>
       </c>
       <c r="J72" t="n">
-        <v>24.3738</v>
+        <v>24.8184</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.7</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3059</v>
+        <v>1.3288</v>
       </c>
       <c r="J73" t="n">
-        <v>23.5062</v>
+        <v>23.9184</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.64</v>
       </c>
       <c r="I74" t="n">
-        <v>1.2329</v>
+        <v>1.2538</v>
       </c>
       <c r="J74" t="n">
-        <v>22.1922</v>
+        <v>22.5684</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.39</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8776</v>
       </c>
       <c r="J75" t="n">
-        <v>15.8688</v>
+        <v>15.7968</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.26</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6029</v>
       </c>
       <c r="J76" t="n">
-        <v>11.259</v>
+        <v>10.8522</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.03</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3957</v>
+        <v>0.4656</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1226</v>
+        <v>8.380800000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.4</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5456</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.8208</v>
+        <v>-9.898199999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.31</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6274</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-11.2932</v>
+        <v>-11.5488</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.31</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6274</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.2932</v>
+        <v>-11.5488</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.28</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6552</v>
+        <v>-0.6741</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.7936</v>
+        <v>-12.1338</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.49</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0926</v>
+        <v>1.1032</v>
       </c>
       <c r="J82" t="n">
-        <v>27.315</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.34</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8129</v>
       </c>
       <c r="J83" t="n">
-        <v>20.88</v>
+        <v>20.3225</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.503</v>
+        <v>0.4679</v>
       </c>
       <c r="J84" t="n">
-        <v>12.575</v>
+        <v>11.6975</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4581</v>
+        <v>0.423</v>
       </c>
       <c r="J85" t="n">
-        <v>11.4525</v>
+        <v>10.575</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.78</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6691</v>
+        <v>-0.6378</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.7275</v>
+        <v>-15.945</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.12</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3713</v>
+        <v>0.3297</v>
       </c>
       <c r="J87" t="n">
-        <v>9.282500000000001</v>
+        <v>8.2425</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2168</v>
+        <v>0.1836</v>
       </c>
       <c r="J88" t="n">
-        <v>5.42</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3583</v>
+        <v>-0.3443</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.9575</v>
+        <v>-8.6075</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5381</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.37</v>
+        <v>-13.4525</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.46</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5381</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.37</v>
+        <v>-13.4525</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4805</v>
+        <v>0.438</v>
       </c>
       <c r="J92" t="n">
-        <v>13.9345</v>
+        <v>12.702</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4047</v>
+        <v>0.3616</v>
       </c>
       <c r="J93" t="n">
-        <v>11.7363</v>
+        <v>10.4864</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0468</v>
       </c>
       <c r="J94" t="n">
-        <v>1.8879</v>
+        <v>1.3572</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0949</v>
+        <v>-0.0743</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.7521</v>
+        <v>-2.1547</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1111</v>
+        <v>-1.121</v>
       </c>
       <c r="J96" t="n">
-        <v>-32.2219</v>
+        <v>-32.509</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.55</v>
       </c>
       <c r="I97" t="n">
-        <v>0.953</v>
+        <v>0.9121</v>
       </c>
       <c r="J97" t="n">
-        <v>27.637</v>
+        <v>26.4509</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2457</v>
+        <v>0.2007</v>
       </c>
       <c r="J98" t="n">
-        <v>7.1253</v>
+        <v>5.8203</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1204</v>
+        <v>0.092</v>
       </c>
       <c r="J99" t="n">
-        <v>3.4916</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.5579</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.5579</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6897</v>
+        <v>0.6555</v>
       </c>
       <c r="J102" t="n">
-        <v>24.8292</v>
+        <v>23.598</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2811</v>
+        <v>0.2426</v>
       </c>
       <c r="J103" t="n">
-        <v>10.1196</v>
+        <v>8.733599999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0552</v>
+        <v>0.0411</v>
       </c>
       <c r="J104" t="n">
-        <v>1.9872</v>
+        <v>1.4796</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1045</v>
+        <v>-0.0799</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.762</v>
+        <v>-2.8764</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4998</v>
+        <v>-0.4576</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.9928</v>
+        <v>-16.4736</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2866</v>
+        <v>0.237</v>
       </c>
       <c r="J107" t="n">
-        <v>10.3176</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1827</v>
+        <v>0.1432</v>
       </c>
       <c r="J108" t="n">
-        <v>6.5772</v>
+        <v>5.1552</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.16</v>
+        <v>0.1234</v>
       </c>
       <c r="J109" t="n">
-        <v>5.76</v>
+        <v>4.4424</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.285</v>
+        <v>-0.2662</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.26</v>
+        <v>-9.5832</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3597</v>
+        <v>-0.3454</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.9492</v>
+        <v>-12.4344</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2933</v>
+        <v>0.2464</v>
       </c>
       <c r="J112" t="n">
-        <v>7.9191</v>
+        <v>6.6528</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.96</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0582</v>
+        <v>-0.0475</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.5714</v>
+        <v>-1.2825</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.9</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1344</v>
+        <v>-0.1186</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.6288</v>
+        <v>-3.2022</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4045</v>
+        <v>-0.3934</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.9215</v>
+        <v>-10.6218</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4045</v>
+        <v>-0.3934</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.9215</v>
+        <v>-10.6218</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8719</v>
+        <v>0.8512</v>
       </c>
       <c r="J117" t="n">
-        <v>23.5413</v>
+        <v>22.9824</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.33</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8314</v>
+        <v>0.8075</v>
       </c>
       <c r="J118" t="n">
-        <v>22.4478</v>
+        <v>21.8025</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7699</v>
+        <v>0.7415</v>
       </c>
       <c r="J119" t="n">
-        <v>20.7873</v>
+        <v>20.0205</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4689</v>
+        <v>-0.4271</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.6603</v>
+        <v>-11.5317</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.78</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6576</v>
+        <v>-0.6239</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.7552</v>
+        <v>-16.8453</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3627</v>
+        <v>0.3018</v>
       </c>
       <c r="J122" t="n">
-        <v>10.881</v>
+        <v>9.054</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2758</v>
+        <v>0.2227</v>
       </c>
       <c r="J123" t="n">
-        <v>8.273999999999999</v>
+        <v>6.681</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2628</v>
+        <v>0.2111</v>
       </c>
       <c r="J124" t="n">
-        <v>7.884</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1957</v>
+        <v>-0.175</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.871</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2167</v>
+        <v>-0.1962</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.501</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.16</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2973</v>
+        <v>0.2855</v>
       </c>
       <c r="J127" t="n">
-        <v>8.919</v>
+        <v>8.565</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1924</v>
+        <v>0.1753</v>
       </c>
       <c r="J128" t="n">
-        <v>5.772</v>
+        <v>5.259</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.207</v>
+        <v>-2.721</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2365</v>
+        <v>-0.2164</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.095</v>
+        <v>-6.492</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.351</v>
+        <v>-0.336</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.53</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.96</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0217</v>
+        <v>-0.0053</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.4557</v>
+        <v>-0.1113</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.77</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2473</v>
+        <v>-0.2332</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.1933</v>
+        <v>-4.8972</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.57</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4282</v>
+        <v>-0.4196</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.9922</v>
+        <v>-8.8116</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4546</v>
+        <v>-0.4482</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.5466</v>
+        <v>-9.4122</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4898</v>
+        <v>-0.4868</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.2858</v>
+        <v>-10.2228</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.7</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3417</v>
+        <v>1.3632</v>
       </c>
       <c r="J137" t="n">
-        <v>28.1757</v>
+        <v>28.6272</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9941</v>
+        <v>0.9933</v>
       </c>
       <c r="J138" t="n">
-        <v>20.8761</v>
+        <v>20.8593</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8696</v>
+        <v>0.8552</v>
       </c>
       <c r="J139" t="n">
-        <v>18.2616</v>
+        <v>17.9592</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2085</v>
+        <v>0.1792</v>
       </c>
       <c r="J140" t="n">
-        <v>4.3785</v>
+        <v>3.7632</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0837</v>
+        <v>0.0626</v>
       </c>
       <c r="J141" t="n">
-        <v>1.7577</v>
+        <v>1.3146</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4718</v>
       </c>
       <c r="J142" t="n">
-        <v>18.4896</v>
+        <v>16.9848</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0978</v>
+        <v>0.0756</v>
       </c>
       <c r="J143" t="n">
-        <v>3.5208</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0576</v>
+        <v>0.0423</v>
       </c>
       <c r="J144" t="n">
-        <v>2.0736</v>
+        <v>1.5228</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.95</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2024</v>
+        <v>-0.1675</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.2864</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3175</v>
+        <v>-0.2761</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.43</v>
+        <v>-9.9396</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3155</v>
+        <v>0.2637</v>
       </c>
       <c r="J147" t="n">
-        <v>11.358</v>
+        <v>9.4932</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1039</v>
+        <v>0.0765</v>
       </c>
       <c r="J148" t="n">
-        <v>3.7404</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J149" t="n">
-        <v>1.6776</v>
+        <v>1.1232</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1777</v>
+        <v>-0.1574</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.3972</v>
+        <v>-5.6664</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2298</v>
+        <v>-0.2094</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.2728</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.49</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0967</v>
+        <v>1.1077</v>
       </c>
       <c r="J152" t="n">
-        <v>25.2241</v>
+        <v>25.4771</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.634</v>
+        <v>0.6004</v>
       </c>
       <c r="J153" t="n">
-        <v>14.582</v>
+        <v>13.8092</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5698</v>
+        <v>0.5346</v>
       </c>
       <c r="J154" t="n">
-        <v>13.1054</v>
+        <v>12.2958</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0312</v>
+        <v>0.0213</v>
       </c>
       <c r="J155" t="n">
-        <v>0.7176</v>
+        <v>0.4899</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3482</v>
+        <v>-0.3069</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.008599999999999</v>
+        <v>-7.0587</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.05</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1868</v>
+        <v>0.1497</v>
       </c>
       <c r="J157" t="n">
-        <v>4.2964</v>
+        <v>3.4431</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0419</v>
+        <v>-0.0327</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.9637</v>
+        <v>-0.7521</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2364</v>
+        <v>-0.218</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.4372</v>
+        <v>-5.014</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.303</v>
+        <v>-0.2856</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.969</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.6</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4212</v>
+        <v>-0.4117</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.6876</v>
+        <v>-9.469099999999999</v>
       </c>
     </row>
   </sheetData>
